--- a/runac/demo/MPJ_DAE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/runac/demo/MPJ_DAE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -303,7 +303,7 @@
 Informar el número de DNI del adolescente, sin puntos ni espacios.
 Qué se espera: texto
 Máximo 15 caracteres.
-Campo obligatorio.</t>
+No es obligatorio.</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
@@ -656,7 +656,7 @@
         <t>Nº DNI
 Qué se espera: texto
 Máximo 15 caracteres.
-Campo obligatorio.</t>
+No es obligatorio.</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
@@ -1343,9 +1343,9 @@
           <t>Situación de documentación</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Nº DNI *</t>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Nº DNI</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -8366,9 +8366,9 @@
           <t>Situación de documentación</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Nº DNI *</t>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Nº DNI</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -16428,8 +16428,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Informar el número de DNI del adolescente, sin puntos ni espacios.
-Campo obligatorio.</t>
+          <t>Informar el número de DNI del adolescente, sin puntos ni espacios.</t>
         </is>
       </c>
     </row>
@@ -16928,11 +16927,7 @@
           <t>Nº DNI</t>
         </is>
       </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
+      <c r="B58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">

--- a/runac/demo/MPJ_DAE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/runac/demo/MPJ_DAE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -8294,7 +8294,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Relevamiento Dispositivos Penales Juveniles</t>
+          <t>Relevamiento CAD y Guardia en Comisaría</t>
         </is>
       </c>
     </row>

--- a/runac/demo/MPJ_DAE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/runac/demo/MPJ_DAE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -921,7 +921,7 @@
       <text>
         <t>Edad al ingreso
 Consignar la edad del adolescente a la fecha del ingreso al dispositivo.
-Qué se espera: una fecha, con formato dd/mm/aaaa
+Qué se espera: un número entero
 No es obligatorio.</t>
       </text>
     </comment>
@@ -8713,8 +8713,8 @@
           <t>Juzgado Penal Juvenil</t>
         </is>
       </c>
-      <c r="AP4" s="5" t="n">
-        <v>45933</v>
+      <c r="AP4" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -8907,8 +8907,8 @@
           <t>Juzgado de Familia N° 2</t>
         </is>
       </c>
-      <c r="AP5" s="5" t="n">
-        <v>45736</v>
+      <c r="AP5" s="6" t="n">
+        <v>11</v>
       </c>
       <c r="AQ5" t="inlineStr"/>
     </row>
@@ -9093,8 +9093,8 @@
           <t>Defensoría de Niñez</t>
         </is>
       </c>
-      <c r="AP6" s="5" t="n">
-        <v>45998</v>
+      <c r="AP6" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="AQ6" t="inlineStr"/>
     </row>
@@ -9288,18 +9288,14 @@
           <t>Asesoría de Familia e Incapaces</t>
         </is>
       </c>
-      <c r="AP7" s="5" t="n">
-        <v>45905</v>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 4</t>
-        </is>
-      </c>
+      <c r="AP7" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>45766</v>
+        <v>45736</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9308,22 +9304,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Centro de Admisión y Derivación</t>
+          <t>Guardia en Comisaría</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Ministerio de Desarrollo Social</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Río Mayo</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -9487,8 +9483,8 @@
           <t>Defensoría de Niñez</t>
         </is>
       </c>
-      <c r="AP8" s="5" t="n">
-        <v>46254</v>
+      <c r="AP8" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
@@ -9681,8 +9677,8 @@
           <t>Juzgado Penal Juvenil</t>
         </is>
       </c>
-      <c r="AP9" s="5" t="n">
-        <v>45722</v>
+      <c r="AP9" s="6" t="n">
+        <v>11</v>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
@@ -9880,18 +9876,14 @@
           <t>Juzgado Penal Juvenil</t>
         </is>
       </c>
-      <c r="AP10" s="5" t="n">
-        <v>46036</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 7</t>
-        </is>
-      </c>
+      <c r="AP10" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45948</v>
+        <v>45677</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -9900,7 +9892,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9910,12 +9902,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Ministerio de Desarrollo Social</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rawson</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -9925,22 +9917,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Sofía</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Posee N° doc. Extranjero</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>90001163</t>
+          <t>Sin inscripción</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -10079,14 +10066,14 @@
           <t>Juzgado de Familia N° 1</t>
         </is>
       </c>
-      <c r="AP11" s="5" t="n">
-        <v>46197</v>
+      <c r="AP11" s="6" t="n">
+        <v>17</v>
       </c>
       <c r="AQ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46150</v>
+        <v>46128</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -10095,22 +10082,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dispositivo no declarado</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Guardia en Comisaría</t>
+          <t>Centro de Admisión y Derivación</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Convenio con organización civil</t>
+          <t>Subsecretaría de Niñez y Adolescencia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -10120,12 +10107,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Rodríguez</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Benjamín</t>
+          <t>Joaquín</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -10135,7 +10122,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>90001310</t>
+          <t>90001274</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -10145,28 +10132,28 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Bhután</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="N12" s="5" t="n">
-        <v>46590</v>
+        <v>42352</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nunca asistió</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Terciario incompleto</t>
+          <t>Terciario completo</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -10176,27 +10163,27 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Visual</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Obra social privada</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -10206,12 +10193,12 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Presunto delito/flagrancia</t>
+          <t>Vulneración de derechos</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -10220,24 +10207,24 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45794</v>
+        <v>45839</v>
       </c>
       <c r="AD12" s="5" t="n">
-        <v>46211</v>
+        <v>45817</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Policía Municipal</t>
+          <t>Gendarmería</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>Comisaría 1ª</t>
+          <t>División Minoridad</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Rawson</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -10247,14 +10234,14 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Hasta 12 hs</t>
+          <t>Entre 7 y 15 días</t>
         </is>
       </c>
       <c r="AJ12" s="5" t="n">
-        <v>45985</v>
+        <v>45946</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>45984</v>
+        <v>46285</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -10262,7 +10249,7 @@
         </is>
       </c>
       <c r="AM12" s="5" t="n">
-        <v>45828</v>
+        <v>45879</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
@@ -10271,21 +10258,17 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Juzgado de Familia N° 1</t>
-        </is>
-      </c>
-      <c r="AP12" s="5" t="n">
-        <v>45679</v>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 9</t>
-        </is>
-      </c>
+          <t>Defensoría de Niñez</t>
+        </is>
+      </c>
+      <c r="AP12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>45704</v>
+        <v>46192</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -10294,22 +10277,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Centro de Admisión y Derivación</t>
+          <t>Guardia en Comisaría</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -10319,12 +10302,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -10334,7 +10317,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>90001424</t>
+          <t>90001386</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -10344,14 +10327,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Martinica</t>
         </is>
       </c>
       <c r="N13" s="5" t="n">
-        <v>42638</v>
+        <v>42479</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -10360,123 +10343,127 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Jardín de infantes</t>
+          <t>Universitario completo</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Qom</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Presunto delito/flagrancia</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Lesiones leves</t>
+        </is>
+      </c>
+      <c r="AC13" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="AD13" s="5" t="n">
+        <v>45688</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Gendarmería</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Comisaría 3ª</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Biedma</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Auditiva</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>IOMA</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Presunto delito/flagrancia</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Hurto simple</t>
-        </is>
-      </c>
-      <c r="AC13" s="5" t="n">
-        <v>45994</v>
-      </c>
-      <c r="AD13" s="5" t="n">
-        <v>45692</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>Gendarmería</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>División Minoridad</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>Cushamen</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Entre 2 y 3 meses</t>
+          <t>Hasta 12 hs</t>
         </is>
       </c>
       <c r="AJ13" s="5" t="n">
-        <v>46167</v>
+        <v>46263</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>46159</v>
+        <v>46280</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Mayoría de edad</t>
+          <t>Dispositivo de privación</t>
         </is>
       </c>
       <c r="AM13" s="5" t="n">
-        <v>46001</v>
+        <v>46203</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Juzgado Penal Juvenil</t>
-        </is>
-      </c>
-      <c r="AP13" s="5" t="n">
-        <v>46250</v>
+          <t>Asesoría de Familia e Incapaces</t>
+        </is>
+      </c>
+      <c r="AP13" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="AQ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46000</v>
+        <v>45705</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -10485,22 +10472,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Guardia en Comisaría</t>
+          <t>Centro de Admisión y Derivación</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rawson</t>
+          <t>Río Mayo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -10510,7 +10497,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -10520,79 +10507,83 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>No posee N° DNI</t>
+          <t>Sin inscripción</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Azerbayán</t>
+          <t>Comoras</t>
         </is>
       </c>
       <c r="N14" s="5" t="n">
-        <v>40760</v>
+        <v>41298</v>
       </c>
       <c r="O14" s="6" t="n">
         <v>14</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sí asiste</t>
+          <t>Nunca asistió</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Jardín de infantes</t>
+          <t>Secundaria incompleta</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Prepaga</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Mapuche</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Motora</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Obra social privada</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Presunto delito/flagrancia</t>
+          <t>Vulneración de derechos</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -10601,49 +10592,49 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>45947</v>
+        <v>46248</v>
       </c>
       <c r="AD14" s="5" t="n">
-        <v>45698</v>
+        <v>46186</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Policía Municipal</t>
+          <t>Gendarmería</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Comisaría 1ª</t>
+          <t>División Minoridad</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Escalante</t>
+          <t>Biedma</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Entre 2 y 3 meses</t>
+          <t>Entre 3 y 7 días</t>
         </is>
       </c>
       <c r="AJ14" s="5" t="n">
-        <v>45960</v>
+        <v>46280</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>46120</v>
+        <v>46280</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Egreso en el domicilio</t>
+          <t>Dispositivo de restricción</t>
         </is>
       </c>
       <c r="AM14" s="5" t="n">
-        <v>46017</v>
+        <v>46280</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
@@ -10652,21 +10643,17 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Defensoría de Niñez</t>
-        </is>
-      </c>
-      <c r="AP14" s="5" t="n">
-        <v>45782</v>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 11</t>
-        </is>
-      </c>
+          <t>Asesoría de Familia e Incapaces</t>
+        </is>
+      </c>
+      <c r="AP14" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46059</v>
+        <v>46118</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -10685,12 +10672,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Servicio de Protección de Derechos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gaiman</t>
+          <t>Trelew</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -10700,12 +10687,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Benjamín</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -10720,105 +10707,109 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Letonia</t>
+          <t>Moldavia</t>
         </is>
       </c>
       <c r="N15" s="5" t="n">
-        <v>41442</v>
+        <v>46354</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>No asiste pero asistió</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Secundaria completa</t>
+          <t>Jardín de infantes</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Visceral</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Prepaga</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Mapuche</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Averiguación de antecedentes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Infracción a la ley de estupefacientes</t>
+        </is>
+      </c>
+      <c r="AC15" s="5" t="n">
+        <v>46223</v>
+      </c>
+      <c r="AD15" s="5" t="n">
+        <v>46272</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Gendarmería</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Comisaría de la Mujer</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Escalante</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Auditiva</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>IOMA</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Presunto delito/flagrancia</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Hurto simple</t>
-        </is>
-      </c>
-      <c r="AC15" s="5" t="n">
-        <v>46272</v>
-      </c>
-      <c r="AD15" s="5" t="n">
-        <v>45770</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>Comisaría 3ª</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>Escalante</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Entre 1 y 2 meses</t>
+          <t>Entre 48 y 72 hs</t>
         </is>
       </c>
       <c r="AJ15" s="5" t="n">
@@ -10829,30 +10820,30 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Mayoría de edad</t>
+          <t>Egreso en el domicilio</t>
         </is>
       </c>
       <c r="AM15" s="5" t="n">
-        <v>46280</v>
+        <v>46225</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Juzgado Penal Juvenil</t>
-        </is>
-      </c>
-      <c r="AP15" s="5" t="n">
-        <v>46206</v>
+          <t>Defensoría de Niñez</t>
+        </is>
+      </c>
+      <c r="AP15" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="AQ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>46236</v>
+        <v>45890</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -10861,7 +10852,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10871,12 +10862,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Río Mayo</t>
+          <t>Rada Tilly</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -10886,43 +10877,48 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>DNI en trámite</t>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>90001826</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Islandia</t>
         </is>
       </c>
       <c r="N16" s="5" t="n">
-        <v>41835</v>
+        <v>40352</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí asiste</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Primaria completa</t>
+          <t>Terciario incompleto</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -10937,116 +10933,112 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Motora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sin cobertura</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Qom</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Averiguación de antecedentes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Hurto simple</t>
+        </is>
+      </c>
+      <c r="AC16" s="5" t="n">
+        <v>45947</v>
+      </c>
+      <c r="AD16" s="5" t="n">
+        <v>46104</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Comisaría de la Mujer</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Rawson</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Hasta 12 hs</t>
+        </is>
+      </c>
+      <c r="AJ16" s="5" t="n">
+        <v>46010</v>
+      </c>
+      <c r="AK16" s="5" t="n">
+        <v>46059</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AM16" s="5" t="n">
+        <v>46050</v>
+      </c>
+      <c r="AN16" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Qom</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Averiguación de antecedentes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Hurto simple</t>
-        </is>
-      </c>
-      <c r="AC16" s="5" t="n">
-        <v>46030</v>
-      </c>
-      <c r="AD16" s="5" t="n">
-        <v>45833</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>Comisaría 1ª</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>Biedma</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AJ16" s="5" t="n">
-        <v>46117</v>
-      </c>
-      <c r="AK16" s="5" t="n">
-        <v>46087</v>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Dispositivo de privación</t>
-        </is>
-      </c>
-      <c r="AM16" s="5" t="n">
-        <v>46230</v>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>Juzgado de Familia N° 1</t>
         </is>
       </c>
-      <c r="AP16" s="5" t="n">
-        <v>45757</v>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 13</t>
-        </is>
-      </c>
+      <c r="AP16" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46163</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -11055,22 +11047,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Centro de Admisión y Derivación</t>
+          <t>Guardia en Comisaría</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Ministerio de Desarrollo Social</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Trelew</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -11080,17 +11072,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sin inscripción</t>
+          <t>Posee N° DNI</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>90001985</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -11100,14 +11097,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Bielorrusia</t>
+          <t>Turkmenistán</t>
         </is>
       </c>
       <c r="N17" s="5" t="n">
-        <v>40778</v>
+        <v>41610</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -11116,12 +11113,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Pre escolar</t>
+          <t>Primaria incompleta</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -11131,12 +11128,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Visual</t>
+          <t>Auditiva</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -11146,43 +11143,43 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Prepaga</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Mapuche-Tehuelche</t>
+          <t>Nota de ejemplo 14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Presunto delito</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Infracción a la ley de estupefacientes</t>
+          <t>Amenazas</t>
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45820</v>
+        <v>45774</v>
       </c>
       <c r="AD17" s="5" t="n">
-        <v>45582</v>
+        <v>45804</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Infantería</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -11192,55 +11189,51 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Escalante</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Hasta 12 hs</t>
+          <t>Entre 15 y 30 días</t>
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
-        <v>45941</v>
+        <v>45792</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>45934</v>
+        <v>45895</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Dispositivo de restricción</t>
+          <t>Abandono/fuga</t>
         </is>
       </c>
       <c r="AM17" s="5" t="n">
-        <v>45891</v>
+        <v>45936</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Juzgado de Familia N° 1</t>
-        </is>
-      </c>
-      <c r="AP17" s="5" t="n">
-        <v>45919</v>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 14</t>
-        </is>
-      </c>
+          <t>Juzgado Penal Juvenil</t>
+        </is>
+      </c>
+      <c r="AP17" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>45807</v>
+        <v>46204</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -11249,22 +11242,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Centro de Admisión y Derivación</t>
+          <t>Guardia en Comisaría</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Rawson</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -11274,22 +11267,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Posee N° DNI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>90002137</t>
+          <t>90002091</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -11299,14 +11292,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="N18" s="5" t="n">
-        <v>42612</v>
+        <v>40548</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -11331,6 +11324,11 @@
       <c r="T18" t="inlineStr">
         <is>
           <t>Sí</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Visual</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -11400,41 +11398,37 @@
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
-        <v>45975</v>
+        <v>46384</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>45814</v>
+        <v>45856</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Mayoría de edad</t>
+          <t>Abandono/fuga</t>
         </is>
       </c>
       <c r="AM18" s="5" t="n">
-        <v>45958</v>
+        <v>45905</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Juzgado de Familia N° 1</t>
-        </is>
-      </c>
-      <c r="AP18" s="5" t="n">
-        <v>46026</v>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 15</t>
-        </is>
-      </c>
+          <t>Asesoría de Familia e Incapaces</t>
+        </is>
+      </c>
+      <c r="AP18" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45831</v>
+        <v>45907</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -11443,22 +11437,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Centro de Admisión y Derivación</t>
+          <t>Guardia en Comisaría</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -11468,22 +11462,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Rodríguez</t>
+          <t>Ojeda</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Posee N° doc. Extranjero</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>90002235</t>
+          <t>Sin inscripción</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -11622,8 +11611,8 @@
           <t>Juzgado de Familia N° 1</t>
         </is>
       </c>
-      <c r="AP19" s="5" t="n">
-        <v>45962</v>
+      <c r="AP19" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
@@ -11812,14 +11801,10 @@
           <t>Asesoría de Familia e Incapaces</t>
         </is>
       </c>
-      <c r="AP20" s="5" t="n">
-        <v>46110</v>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 17</t>
-        </is>
-      </c>
+      <c r="AP20" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -11960,46 +11945,46 @@
         <v>46226</v>
       </c>
       <c r="AD21" s="5" t="n">
-        <v>45623</v>
+        <v>46367</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Prefectura</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>Comisaría de la Mujer</t>
+          <t>Comisaría 1ª</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>Cushamen</t>
+          <t>Escalante</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Entre 15 y 30 días</t>
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
         <v>46280</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>46258</v>
+        <v>46264</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Dispositivo de restricción</t>
+          <t>Egreso familia + Sistema Protección</t>
         </is>
       </c>
       <c r="AM21" s="5" t="n">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
@@ -12008,21 +11993,17 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Juzgado Penal Juvenil</t>
-        </is>
-      </c>
-      <c r="AP21" s="5" t="n">
-        <v>45819</v>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 18</t>
-        </is>
-      </c>
+          <t>Defensoría de Niñez</t>
+        </is>
+      </c>
+      <c r="AP21" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>46129</v>
+        <v>46252</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -12041,12 +12022,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Rada Tilly</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -12056,60 +12037,65 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>DNI en trámite</t>
+          <t>Posee N° doc. Extranjero</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>90002613</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="N22" s="5" t="n">
-        <v>41802</v>
+        <v>40294</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nunca asistió</t>
+          <t>Sí asiste</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Primaria incompleta</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>Auditiva</t>
@@ -12127,92 +12113,92 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 19</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Presunto delito/flagrancia</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Robo en grado de tentativa</t>
+          <t>Amenazas</t>
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>46139</v>
+        <v>45799</v>
       </c>
       <c r="AD22" s="5" t="n">
-        <v>46240</v>
+        <v>45820</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Prefectura</t>
+          <t>Policía Provincial</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>División Minoridad</t>
+          <t>Comisaría 1ª</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>Escalante</t>
+          <t>Rawson</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Entre 15 y 30 días</t>
+          <t>Entre 24 y 48 hs</t>
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
-        <v>46254</v>
+        <v>45838</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>46280</v>
+        <v>45940</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Egreso con familia/referente</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AM22" s="5" t="n">
-        <v>46160</v>
+        <v>45935</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Juzgado Penal Juvenil</t>
-        </is>
-      </c>
-      <c r="AP22" s="5" t="n">
-        <v>46059</v>
+          <t>Juzgado de Familia N° 1</t>
+        </is>
+      </c>
+      <c r="AP22" s="6" t="n">
+        <v>15</v>
       </c>
       <c r="AQ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45718</v>
+        <v>46036</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -12221,12 +12207,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Guardia en Comisaría</t>
+          <t>Centro de Admisión y Derivación</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -12236,7 +12222,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>Puerto Madryn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -12246,34 +12232,39 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Rodríguez</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>DNI en trámite</t>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>90002819</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Eslovaquia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="N23" s="5" t="n">
-        <v>41898</v>
+        <v>40633</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -12282,19 +12273,19 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Jardín de infantes</t>
+          <t>Universitario incompleto</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -12307,106 +12298,98 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sin cobertura</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Contravención</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Infracción a la ley de estupefacientes</t>
+        </is>
+      </c>
+      <c r="AC23" s="5" t="n">
+        <v>45918</v>
+      </c>
+      <c r="AD23" s="5" t="n">
+        <v>46033</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Comisaría 3ª</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Rawson</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Sin cobertura</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Entre 3 y 7 días</t>
+        </is>
+      </c>
+      <c r="AJ23" s="5" t="n">
+        <v>45936</v>
+      </c>
+      <c r="AK23" s="5" t="n">
+        <v>46053</v>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Mayoría de edad</t>
+        </is>
+      </c>
+      <c r="AM23" s="5" t="n">
+        <v>46048</v>
+      </c>
+      <c r="AN23" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 20</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Vulneración de derechos</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Robo en grado de tentativa</t>
-        </is>
-      </c>
-      <c r="AC23" s="5" t="n">
-        <v>45981</v>
-      </c>
-      <c r="AD23" s="5" t="n">
-        <v>45840</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>Policía Provincial</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>Comisaría de la Mujer</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>Escalante</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Entre 7 y 15 días</t>
-        </is>
-      </c>
-      <c r="AJ23" s="5" t="n">
-        <v>46029</v>
-      </c>
-      <c r="AK23" s="5" t="n">
-        <v>46152</v>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Egreso en el domicilio</t>
-        </is>
-      </c>
-      <c r="AM23" s="5" t="n">
-        <v>46116</v>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Juzgado de Familia N° 1</t>
-        </is>
-      </c>
-      <c r="AP23" s="5" t="n">
-        <v>45741</v>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 20</t>
-        </is>
-      </c>
+          <t>Asesoría de Familia e Incapaces</t>
+        </is>
+      </c>
+      <c r="AP23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>46259</v>
+        <v>46671</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -12415,7 +12398,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -12425,12 +12408,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Ministerio de Desarrollo Social</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>El Maitén</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -12440,17 +12423,22 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>DNI en trámite</t>
+          <t>Posee N° DNI</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>90002951</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -12460,53 +12448,53 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Santa Elena</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="N24" s="5" t="n">
-        <v>40455</v>
+        <v>40360</v>
       </c>
       <c r="O24" s="6" t="n">
         <v>8</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>No asiste pero asistió</t>
+          <t>Nunca asistió</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Universitario completo</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>IOMA</t>
+          <t>Sin cobertura</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -12517,33 +12505,33 @@
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Presunto delito/flagrancia</t>
+          <t>Vulneración de derechos</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Amenazas</t>
+          <t>Daño</t>
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>46100</v>
+        <v>46242</v>
       </c>
       <c r="AD24" s="5" t="n">
-        <v>45804</v>
+        <v>45979</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Gendarmería</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>Comisaría 3ª</t>
+          <t>Comisaría 1ª</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -12558,22 +12546,22 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Entre 3 y 7 días</t>
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
-        <v>46324</v>
+        <v>46280</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>46152</v>
+        <v>46280</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Egreso con familia/referente</t>
+          <t>Egreso familia + Sistema Protección</t>
         </is>
       </c>
       <c r="AM24" s="5" t="n">
-        <v>46181</v>
+        <v>46352</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -12582,17 +12570,17 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Asesoría de Familia e Incapaces</t>
-        </is>
-      </c>
-      <c r="AP24" s="5" t="n">
-        <v>19</v>
+          <t>Juzgado Penal Juvenil</t>
+        </is>
+      </c>
+      <c r="AP24" s="6" t="n">
+        <v>16</v>
       </c>
       <c r="AQ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45832</v>
+        <v>45608</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -12601,7 +12589,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -12611,12 +12599,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12626,89 +12614,98 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Benjamín</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sin inscripción</t>
+          <t>Posee N° doc. Extranjero</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>90003070</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Guinea-Bissau</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>40944</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Secundaria incompleta</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v>42305</v>
-      </c>
-      <c r="O25" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Sí asiste</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>PAMI</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Visceral</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Prepaga</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Contravención</t>
+          <t>Protección de derechos</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -12717,72 +12714,68 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>45603</v>
+        <v>45951</v>
       </c>
       <c r="AD25" s="5" t="n">
-        <v>45977</v>
+        <v>46174</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>Prefectura</t>
+          <t>Policía Municipal</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>División Minoridad</t>
+          <t>Comisaría de la Mujer</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>Cushamen</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Entre 15 y 30 días</t>
+        </is>
+      </c>
+      <c r="AJ25" s="5" t="n">
+        <v>46106</v>
+      </c>
+      <c r="AK25" s="5" t="n">
+        <v>46135</v>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Egreso familia + Sistema Protección</t>
+        </is>
+      </c>
+      <c r="AM25" s="5" t="n">
+        <v>45994</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Entre 7 y 15 días</t>
-        </is>
-      </c>
-      <c r="AJ25" s="5" t="n">
-        <v>45646</v>
-      </c>
-      <c r="AK25" s="5" t="n">
-        <v>45780</v>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Abandono/fuga</t>
-        </is>
-      </c>
-      <c r="AM25" s="5" t="n">
-        <v>45693</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Juzgado de Familia N° 1</t>
-        </is>
-      </c>
-      <c r="AP25" s="5" t="n">
-        <v>45918</v>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 22</t>
-        </is>
-      </c>
+          <t>Defensoría de Niñez</t>
+        </is>
+      </c>
+      <c r="AP25" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45834</v>
+        <v>46236</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -12796,12 +12789,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Centro de Admisión y Derivación</t>
+          <t>Guardia en Comisaría</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Subsecretaría de Niñez y Adolescencia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -12816,163 +12809,168 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Villalba</t>
+          <t>Ojeda</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>DNI en trámite</t>
+          <t>Posee N° DNI</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>90003236</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Yibuti</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="N26" s="5" t="n">
-        <v>40306</v>
+        <v>42280</v>
       </c>
       <c r="O26" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>No asiste pero asistió</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Nunca asistió</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>PAMI</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Amenazas</t>
+        </is>
+      </c>
+      <c r="AC26" s="5" t="n">
+        <v>45904</v>
+      </c>
+      <c r="AD26" s="5" t="n">
+        <v>45909</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Comisaría 1ª</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Cushamen</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Más de 3 meses</t>
+        </is>
+      </c>
+      <c r="AJ26" s="5" t="n">
+        <v>46020</v>
+      </c>
+      <c r="AK26" s="5" t="n">
+        <v>45999</v>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Dispositivo de privación</t>
+        </is>
+      </c>
+      <c r="AM26" s="5" t="n">
+        <v>46018</v>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Asesoría de Familia e Incapaces</t>
+        </is>
+      </c>
+      <c r="AP26" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Nunca asistió</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Obra social provincial</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
+      <c r="AQ26" t="inlineStr">
         <is>
           <t>Nota de ejemplo 23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Protección de derechos</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>Robo en grado de tentativa</t>
-        </is>
-      </c>
-      <c r="AC26" s="5" t="n">
-        <v>45584</v>
-      </c>
-      <c r="AD26" s="5" t="n">
-        <v>45819</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>Infantería</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>Comisaría de la Mujer</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>Biedma</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Entre 2 y 3 meses</t>
-        </is>
-      </c>
-      <c r="AJ26" s="5" t="n">
-        <v>45620</v>
-      </c>
-      <c r="AK26" s="5" t="n">
-        <v>45720</v>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>Dispositivo de privación</t>
-        </is>
-      </c>
-      <c r="AM26" s="5" t="n">
-        <v>45686</v>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Juzgado Penal Juvenil</t>
-        </is>
-      </c>
-      <c r="AP26" s="5" t="n">
-        <v>46024</v>
-      </c>
-      <c r="AQ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46089</v>
+        <v>45958</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -12981,22 +12979,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Guardia en Comisaría</t>
+          <t>Centro de Admisión y Derivación</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Convenio con organización civil</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trelew</t>
+          <t>Rawson</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13006,17 +13004,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Rodríguez</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Sofía</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>DNI en trámite</t>
+          <t>Posee N° doc. Extranjero</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>90003354</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -13026,48 +13029,48 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="N27" s="5" t="n">
-        <v>41348</v>
+        <v>42479</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Nunca asistió</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Primaria incompleta</t>
+          <t>Primaria completa</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>Visceral</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -13083,86 +13086,82 @@
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Presunto delito</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Hurto simple</t>
+        </is>
+      </c>
+      <c r="AC27" s="5" t="n">
+        <v>45817</v>
+      </c>
+      <c r="AD27" s="5" t="n">
+        <v>46103</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Comisaría 1ª</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>Lesiones leves</t>
-        </is>
-      </c>
-      <c r="AC27" s="5" t="n">
-        <v>45596</v>
-      </c>
-      <c r="AD27" s="5" t="n">
-        <v>45924</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>Policía Municipal</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>Comisaría de la Mujer</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>Futaleufú</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Entre 3 y 7 días</t>
         </is>
       </c>
       <c r="AJ27" s="5" t="n">
-        <v>45778</v>
+        <v>45999</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>45776</v>
+        <v>45834</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Egreso Sistema Protección</t>
+          <t>Mayoría de edad</t>
         </is>
       </c>
       <c r="AM27" s="5" t="n">
-        <v>45689</v>
+        <v>45956</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Juzgado de Familia N° 2</t>
-        </is>
-      </c>
-      <c r="AP27" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 24</t>
-        </is>
-      </c>
+          <t>Juzgado Penal Juvenil</t>
+        </is>
+      </c>
+      <c r="AP27" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>46147</v>
+        <v>45626</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -13171,22 +13170,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Centro de Admisión y Derivación</t>
+          <t>Guardia en Comisaría</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Esquel</t>
+          <t>Puerto Madryn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13196,105 +13195,106 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Sin inscripción</t>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>90003442</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>San Cristóbal y Nieves</t>
+          <t>Santa Lucía</t>
         </is>
       </c>
       <c r="N28" s="5" t="n">
-        <v>41856</v>
+        <v>42202</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sí asiste</t>
+          <t>Nunca asistió</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Pre escolar</t>
+          <t>Terciario completo</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Motora</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Sin cobertura</t>
+          <t>Prepaga</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Tehuelche</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Vulneración de derechos</t>
+          <t>Averiguación de antecedentes</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Infracción a la ley de estupefacientes</t>
+          <t>Amenazas</t>
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>46093</v>
+        <v>45789</v>
       </c>
       <c r="AD28" s="5" t="n">
-        <v>46147</v>
+        <v>45741</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -13303,17 +13303,17 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>Comisaría 1ª</t>
+          <t>División Minoridad</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>Rawson</t>
+          <t>Cushamen</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
@@ -13322,41 +13322,37 @@
         </is>
       </c>
       <c r="AJ28" s="5" t="n">
-        <v>46171</v>
+        <v>45871</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>46136</v>
+        <v>45954</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Egreso Sistema Protección</t>
+          <t>Egreso en el domicilio</t>
         </is>
       </c>
       <c r="AM28" s="5" t="n">
-        <v>46176</v>
+        <v>45905</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Juzgado de Familia N° 2</t>
-        </is>
-      </c>
-      <c r="AP28" s="5" t="n">
-        <v>45925</v>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 25</t>
-        </is>
-      </c>
+          <t>Asesoría de Familia e Incapaces</t>
+        </is>
+      </c>
+      <c r="AP28" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>45989</v>
+        <v>45715</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -13365,12 +13361,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Guardia en Comisaría</t>
+          <t>Centro de Admisión y Derivación</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -13380,7 +13376,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>El Maitén</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -13395,29 +13391,34 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>No posee N° DNI</t>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>90003569</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="N29" s="5" t="n">
-        <v>42364</v>
+        <v>40805</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -13426,308 +13427,317 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Universitario incompleto</t>
+          <t>Pre escolar</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Vulneración de derechos</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Infracción a la ley de estupefacientes</t>
+        </is>
+      </c>
+      <c r="AC29" s="5" t="n">
+        <v>45998</v>
+      </c>
+      <c r="AD29" s="5" t="n">
+        <v>46151</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Prefectura</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Comisaría 1ª</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Cushamen</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Mapuche</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Contravención</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>Amenazas</t>
-        </is>
-      </c>
-      <c r="AC29" s="5" t="n">
-        <v>45689</v>
-      </c>
-      <c r="AD29" s="5" t="n">
-        <v>46008</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>Gendarmería</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>División Minoridad</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>Cushamen</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Entre 12 y 24 hs</t>
+        </is>
+      </c>
+      <c r="AJ29" s="5" t="n">
+        <v>46150</v>
+      </c>
+      <c r="AK29" s="5" t="n">
+        <v>46147</v>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Egreso Sistema Protección</t>
+        </is>
+      </c>
+      <c r="AM29" s="5" t="n">
+        <v>46042</v>
+      </c>
+      <c r="AN29" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>No corresponde</t>
-        </is>
-      </c>
-      <c r="AJ29" s="5" t="n">
-        <v>45817</v>
-      </c>
-      <c r="AK29" s="5" t="n">
-        <v>45850</v>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Mayoría de edad</t>
-        </is>
-      </c>
-      <c r="AM29" s="5" t="n">
-        <v>45764</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Juzgado Penal Juvenil</t>
-        </is>
-      </c>
-      <c r="AP29" s="5" t="n">
-        <v>45785</v>
-      </c>
-      <c r="AQ29" t="inlineStr"/>
+          <t>Asesoría de Familia e Incapaces</t>
+        </is>
+      </c>
+      <c r="AP29" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 26</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chubut</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Hogar Los Álamos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Centro de Admisión y Derivación</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>El Maitén</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CHU-2026-0027</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ojeda</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Joaquín</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>DNI en trámite</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>San Cristóbal y Nieves</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>42522</v>
+      </c>
+      <c r="O30" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sí asiste</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Terciario incompleto</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Obra social privada</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 27</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Presunto delito/flagrancia</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Daño</t>
+        </is>
+      </c>
+      <c r="AC30" s="5" t="n">
         <v>46205</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Centro de Admisión y Derivación</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Municipalidad de Rawson</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Gaiman</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>CHU-2026-0027</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Díaz</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Benjamín</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>No posee N° DNI</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Guam</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>41486</v>
-      </c>
-      <c r="O30" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Nunca asistió</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Secundaria completa</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Obra social provincial</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Presunto delito/flagrancia</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>Daño</t>
-        </is>
-      </c>
-      <c r="AC30" s="5" t="n">
-        <v>46026</v>
-      </c>
       <c r="AD30" s="5" t="n">
-        <v>46285</v>
+        <v>46218</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>Gendarmería</t>
+          <t>Policía Federal</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>Comisaría 3ª</t>
+          <t>División Minoridad</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Biedma</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Entre 15 y 30 días</t>
         </is>
       </c>
       <c r="AJ30" s="5" t="n">
-        <v>46107</v>
+        <v>46258</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>46075</v>
+        <v>46286</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Egreso Sistema Protección</t>
+          <t>Egreso familia + Sistema Protección</t>
         </is>
       </c>
       <c r="AM30" s="5" t="n">
-        <v>46154</v>
+        <v>46239</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Defensoría de Niñez</t>
-        </is>
-      </c>
-      <c r="AP30" s="5" t="n">
-        <v>45769</v>
+          <t>Asesoría de Familia e Incapaces</t>
+        </is>
+      </c>
+      <c r="AP30" s="6" t="n">
+        <v>11</v>
       </c>
       <c r="AQ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>45770</v>
+        <v>45953</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -13736,22 +13746,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Centro de Admisión y Derivación</t>
+          <t>Guardia en Comisaría</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13776,58 +13786,58 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>41752</v>
+      </c>
+      <c r="O31" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Primaria incompleta</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="n">
-        <v>40386</v>
-      </c>
-      <c r="O31" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Universitario incompleto</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>IOMA</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13838,86 +13848,82 @@
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Averiguación de antecedentes</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Daño</t>
+        </is>
+      </c>
+      <c r="AC31" s="5" t="n">
+        <v>45964</v>
+      </c>
+      <c r="AD31" s="5" t="n">
+        <v>45770</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Policía Provincial</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Comisaría 1ª</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Biedma</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Entre 15 y 30 días</t>
+        </is>
+      </c>
+      <c r="AJ31" s="5" t="n">
+        <v>46026</v>
+      </c>
+      <c r="AK31" s="5" t="n">
+        <v>46020</v>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AM31" s="5" t="n">
+        <v>46055</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Presunto delito/flagrancia</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>Amenazas</t>
-        </is>
-      </c>
-      <c r="AC31" s="5" t="n">
-        <v>45905</v>
-      </c>
-      <c r="AD31" s="5" t="n">
-        <v>45867</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>Infantería</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>Comisaría 1ª</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>Biedma</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Entre 2 y 3 meses</t>
-        </is>
-      </c>
-      <c r="AJ31" s="5" t="n">
-        <v>46049</v>
-      </c>
-      <c r="AK31" s="5" t="n">
-        <v>45955</v>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Dispositivo de privación</t>
-        </is>
-      </c>
-      <c r="AM31" s="5" t="n">
-        <v>46047</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>Juzgado de Familia N° 1</t>
         </is>
       </c>
-      <c r="AP31" s="5" t="n">
-        <v>45884</v>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 28</t>
-        </is>
-      </c>
+      <c r="AP31" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45818</v>
+        <v>45668</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -13926,7 +13932,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -13941,7 +13947,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Maitén</t>
+          <t>Rawson</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13951,7 +13957,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Ledesma</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -13961,33 +13967,38 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>No posee N° DNI</t>
+          <t>Posee N° doc. Extranjero</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>90003990</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="N32" s="5" t="n">
-        <v>41567</v>
+        <v>41677</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nunca asistió</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Pre escolar</t>
+          <t>Secundaria incompleta</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -13997,107 +14008,111 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Visceral</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Obra social provincial</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Motora</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>PAMI</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Mapuche</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Protección de derechos</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Daño</t>
+        </is>
+      </c>
+      <c r="AC32" s="5" t="n">
+        <v>45716</v>
+      </c>
+      <c r="AD32" s="5" t="n">
+        <v>45993</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>Policía Municipal</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Comisaría 3ª</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Rawson</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Entre 3 y 7 días</t>
+        </is>
+      </c>
+      <c r="AJ32" s="5" t="n">
+        <v>45803</v>
+      </c>
+      <c r="AK32" s="5" t="n">
+        <v>45859</v>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Dispositivo de privación</t>
+        </is>
+      </c>
+      <c r="AM32" s="5" t="n">
+        <v>45910</v>
+      </c>
+      <c r="AN32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Presunto delito/flagrancia</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>Daño</t>
-        </is>
-      </c>
-      <c r="AC32" s="5" t="n">
-        <v>45748</v>
-      </c>
-      <c r="AD32" s="5" t="n">
-        <v>45812</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>Policía Federal</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>Comisaría 3ª</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>Futaleufú</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Entre 3 y 7 días</t>
-        </is>
-      </c>
-      <c r="AJ32" s="5" t="n">
-        <v>45790</v>
-      </c>
-      <c r="AK32" s="5" t="n">
-        <v>45849</v>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AM32" s="5" t="n">
-        <v>45938</v>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Asesoría de Familia e Incapaces</t>
-        </is>
-      </c>
-      <c r="AP32" s="5" t="n">
-        <v>45935</v>
+          <t>Juzgado de Familia N° 2</t>
+        </is>
+      </c>
+      <c r="AP32" s="6" t="n">
+        <v>12</v>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
@@ -14107,7 +14122,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>45703</v>
+        <v>46283</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -14116,7 +14131,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -14126,12 +14141,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Ministerio de Desarrollo Social</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14141,22 +14156,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sosa</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Sofía</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Posee N° DNI</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>90004163</t>
+          <t>DNI en trámite</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -14166,139 +14176,139 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Santo Tomé y Príncipe</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="N33" s="5" t="n">
-        <v>40288</v>
+        <v>41788</v>
       </c>
       <c r="O33" s="6" t="n">
         <v>12</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Nunca asistió</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Primaria completa</t>
+          <t>Universitario incompleto</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Visceral</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sin cobertura</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Auditiva</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Mapuche-Tehuelche</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Presunto delito/flagrancia</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Lesiones leves</t>
+        </is>
+      </c>
+      <c r="AC33" s="5" t="n">
+        <v>45590</v>
+      </c>
+      <c r="AD33" s="5" t="n">
+        <v>46167</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Comisaría de la Mujer</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Rawson</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Prepaga</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr">
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Entre 15 y 30 días</t>
+        </is>
+      </c>
+      <c r="AJ33" s="5" t="n">
+        <v>46393</v>
+      </c>
+      <c r="AK33" s="5" t="n">
+        <v>45740</v>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Abandono/fuga</t>
+        </is>
+      </c>
+      <c r="AM33" s="5" t="n">
+        <v>45634</v>
+      </c>
+      <c r="AN33" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Vulneración de derechos</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>Amenazas</t>
-        </is>
-      </c>
-      <c r="AC33" s="5" t="n">
-        <v>45645</v>
-      </c>
-      <c r="AD33" s="5" t="n">
-        <v>46351</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>Gendarmería</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>Comisaría 1ª</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>Biedma</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Entre 7 y 15 días</t>
-        </is>
-      </c>
-      <c r="AJ33" s="5" t="n">
-        <v>46295</v>
-      </c>
-      <c r="AK33" s="5" t="n">
-        <v>45834</v>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Egreso con familia/referente</t>
-        </is>
-      </c>
-      <c r="AM33" s="5" t="n">
-        <v>45826</v>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>Asesoría de Familia e Incapaces</t>
         </is>
       </c>
-      <c r="AP33" s="5" t="n">
-        <v>46067</v>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 30</t>
-        </is>
-      </c>
+      <c r="AP33" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -14309,7 +14319,7 @@
       <c r="AJ34" s="5" t="n"/>
       <c r="AK34" s="5" t="n"/>
       <c r="AM34" s="5" t="n"/>
-      <c r="AP34" s="5" t="n"/>
+      <c r="AP34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -14320,7 +14330,7 @@
       <c r="AJ35" s="5" t="n"/>
       <c r="AK35" s="5" t="n"/>
       <c r="AM35" s="5" t="n"/>
-      <c r="AP35" s="5" t="n"/>
+      <c r="AP35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -14331,7 +14341,7 @@
       <c r="AJ36" s="5" t="n"/>
       <c r="AK36" s="5" t="n"/>
       <c r="AM36" s="5" t="n"/>
-      <c r="AP36" s="5" t="n"/>
+      <c r="AP36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -14342,7 +14352,7 @@
       <c r="AJ37" s="5" t="n"/>
       <c r="AK37" s="5" t="n"/>
       <c r="AM37" s="5" t="n"/>
-      <c r="AP37" s="5" t="n"/>
+      <c r="AP37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -14353,7 +14363,7 @@
       <c r="AJ38" s="5" t="n"/>
       <c r="AK38" s="5" t="n"/>
       <c r="AM38" s="5" t="n"/>
-      <c r="AP38" s="5" t="n"/>
+      <c r="AP38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -14364,7 +14374,7 @@
       <c r="AJ39" s="5" t="n"/>
       <c r="AK39" s="5" t="n"/>
       <c r="AM39" s="5" t="n"/>
-      <c r="AP39" s="5" t="n"/>
+      <c r="AP39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -14375,7 +14385,7 @@
       <c r="AJ40" s="5" t="n"/>
       <c r="AK40" s="5" t="n"/>
       <c r="AM40" s="5" t="n"/>
-      <c r="AP40" s="5" t="n"/>
+      <c r="AP40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -14386,7 +14396,7 @@
       <c r="AJ41" s="5" t="n"/>
       <c r="AK41" s="5" t="n"/>
       <c r="AM41" s="5" t="n"/>
-      <c r="AP41" s="5" t="n"/>
+      <c r="AP41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -14397,7 +14407,7 @@
       <c r="AJ42" s="5" t="n"/>
       <c r="AK42" s="5" t="n"/>
       <c r="AM42" s="5" t="n"/>
-      <c r="AP42" s="5" t="n"/>
+      <c r="AP42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -14408,7 +14418,7 @@
       <c r="AJ43" s="5" t="n"/>
       <c r="AK43" s="5" t="n"/>
       <c r="AM43" s="5" t="n"/>
-      <c r="AP43" s="5" t="n"/>
+      <c r="AP43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -14419,7 +14429,7 @@
       <c r="AJ44" s="5" t="n"/>
       <c r="AK44" s="5" t="n"/>
       <c r="AM44" s="5" t="n"/>
-      <c r="AP44" s="5" t="n"/>
+      <c r="AP44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -14430,7 +14440,7 @@
       <c r="AJ45" s="5" t="n"/>
       <c r="AK45" s="5" t="n"/>
       <c r="AM45" s="5" t="n"/>
-      <c r="AP45" s="5" t="n"/>
+      <c r="AP45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -14441,7 +14451,7 @@
       <c r="AJ46" s="5" t="n"/>
       <c r="AK46" s="5" t="n"/>
       <c r="AM46" s="5" t="n"/>
-      <c r="AP46" s="5" t="n"/>
+      <c r="AP46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -14452,7 +14462,7 @@
       <c r="AJ47" s="5" t="n"/>
       <c r="AK47" s="5" t="n"/>
       <c r="AM47" s="5" t="n"/>
-      <c r="AP47" s="5" t="n"/>
+      <c r="AP47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -14463,7 +14473,7 @@
       <c r="AJ48" s="5" t="n"/>
       <c r="AK48" s="5" t="n"/>
       <c r="AM48" s="5" t="n"/>
-      <c r="AP48" s="5" t="n"/>
+      <c r="AP48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -14474,7 +14484,7 @@
       <c r="AJ49" s="5" t="n"/>
       <c r="AK49" s="5" t="n"/>
       <c r="AM49" s="5" t="n"/>
-      <c r="AP49" s="5" t="n"/>
+      <c r="AP49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -14485,7 +14495,7 @@
       <c r="AJ50" s="5" t="n"/>
       <c r="AK50" s="5" t="n"/>
       <c r="AM50" s="5" t="n"/>
-      <c r="AP50" s="5" t="n"/>
+      <c r="AP50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -14496,7 +14506,7 @@
       <c r="AJ51" s="5" t="n"/>
       <c r="AK51" s="5" t="n"/>
       <c r="AM51" s="5" t="n"/>
-      <c r="AP51" s="5" t="n"/>
+      <c r="AP51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -14507,7 +14517,7 @@
       <c r="AJ52" s="5" t="n"/>
       <c r="AK52" s="5" t="n"/>
       <c r="AM52" s="5" t="n"/>
-      <c r="AP52" s="5" t="n"/>
+      <c r="AP52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -14518,7 +14528,7 @@
       <c r="AJ53" s="5" t="n"/>
       <c r="AK53" s="5" t="n"/>
       <c r="AM53" s="5" t="n"/>
-      <c r="AP53" s="5" t="n"/>
+      <c r="AP53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -14529,7 +14539,7 @@
       <c r="AJ54" s="5" t="n"/>
       <c r="AK54" s="5" t="n"/>
       <c r="AM54" s="5" t="n"/>
-      <c r="AP54" s="5" t="n"/>
+      <c r="AP54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -14540,7 +14550,7 @@
       <c r="AJ55" s="5" t="n"/>
       <c r="AK55" s="5" t="n"/>
       <c r="AM55" s="5" t="n"/>
-      <c r="AP55" s="5" t="n"/>
+      <c r="AP55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
@@ -14551,7 +14561,7 @@
       <c r="AJ56" s="5" t="n"/>
       <c r="AK56" s="5" t="n"/>
       <c r="AM56" s="5" t="n"/>
-      <c r="AP56" s="5" t="n"/>
+      <c r="AP56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -14562,7 +14572,7 @@
       <c r="AJ57" s="5" t="n"/>
       <c r="AK57" s="5" t="n"/>
       <c r="AM57" s="5" t="n"/>
-      <c r="AP57" s="5" t="n"/>
+      <c r="AP57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -14573,7 +14583,7 @@
       <c r="AJ58" s="5" t="n"/>
       <c r="AK58" s="5" t="n"/>
       <c r="AM58" s="5" t="n"/>
-      <c r="AP58" s="5" t="n"/>
+      <c r="AP58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -14584,7 +14594,7 @@
       <c r="AJ59" s="5" t="n"/>
       <c r="AK59" s="5" t="n"/>
       <c r="AM59" s="5" t="n"/>
-      <c r="AP59" s="5" t="n"/>
+      <c r="AP59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
@@ -14595,7 +14605,7 @@
       <c r="AJ60" s="5" t="n"/>
       <c r="AK60" s="5" t="n"/>
       <c r="AM60" s="5" t="n"/>
-      <c r="AP60" s="5" t="n"/>
+      <c r="AP60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
@@ -14606,7 +14616,7 @@
       <c r="AJ61" s="5" t="n"/>
       <c r="AK61" s="5" t="n"/>
       <c r="AM61" s="5" t="n"/>
-      <c r="AP61" s="5" t="n"/>
+      <c r="AP61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -14617,7 +14627,7 @@
       <c r="AJ62" s="5" t="n"/>
       <c r="AK62" s="5" t="n"/>
       <c r="AM62" s="5" t="n"/>
-      <c r="AP62" s="5" t="n"/>
+      <c r="AP62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -14628,7 +14638,7 @@
       <c r="AJ63" s="5" t="n"/>
       <c r="AK63" s="5" t="n"/>
       <c r="AM63" s="5" t="n"/>
-      <c r="AP63" s="5" t="n"/>
+      <c r="AP63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
@@ -14639,7 +14649,7 @@
       <c r="AJ64" s="5" t="n"/>
       <c r="AK64" s="5" t="n"/>
       <c r="AM64" s="5" t="n"/>
-      <c r="AP64" s="5" t="n"/>
+      <c r="AP64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
@@ -14650,7 +14660,7 @@
       <c r="AJ65" s="5" t="n"/>
       <c r="AK65" s="5" t="n"/>
       <c r="AM65" s="5" t="n"/>
-      <c r="AP65" s="5" t="n"/>
+      <c r="AP65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -14661,7 +14671,7 @@
       <c r="AJ66" s="5" t="n"/>
       <c r="AK66" s="5" t="n"/>
       <c r="AM66" s="5" t="n"/>
-      <c r="AP66" s="5" t="n"/>
+      <c r="AP66" s="6" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -14672,7 +14682,7 @@
       <c r="AJ67" s="5" t="n"/>
       <c r="AK67" s="5" t="n"/>
       <c r="AM67" s="5" t="n"/>
-      <c r="AP67" s="5" t="n"/>
+      <c r="AP67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
@@ -14683,7 +14693,7 @@
       <c r="AJ68" s="5" t="n"/>
       <c r="AK68" s="5" t="n"/>
       <c r="AM68" s="5" t="n"/>
-      <c r="AP68" s="5" t="n"/>
+      <c r="AP68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
@@ -14694,7 +14704,7 @@
       <c r="AJ69" s="5" t="n"/>
       <c r="AK69" s="5" t="n"/>
       <c r="AM69" s="5" t="n"/>
-      <c r="AP69" s="5" t="n"/>
+      <c r="AP69" s="6" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -14705,7 +14715,7 @@
       <c r="AJ70" s="5" t="n"/>
       <c r="AK70" s="5" t="n"/>
       <c r="AM70" s="5" t="n"/>
-      <c r="AP70" s="5" t="n"/>
+      <c r="AP70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -14716,7 +14726,7 @@
       <c r="AJ71" s="5" t="n"/>
       <c r="AK71" s="5" t="n"/>
       <c r="AM71" s="5" t="n"/>
-      <c r="AP71" s="5" t="n"/>
+      <c r="AP71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
@@ -14727,7 +14737,7 @@
       <c r="AJ72" s="5" t="n"/>
       <c r="AK72" s="5" t="n"/>
       <c r="AM72" s="5" t="n"/>
-      <c r="AP72" s="5" t="n"/>
+      <c r="AP72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
@@ -14738,7 +14748,7 @@
       <c r="AJ73" s="5" t="n"/>
       <c r="AK73" s="5" t="n"/>
       <c r="AM73" s="5" t="n"/>
-      <c r="AP73" s="5" t="n"/>
+      <c r="AP73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -14749,7 +14759,7 @@
       <c r="AJ74" s="5" t="n"/>
       <c r="AK74" s="5" t="n"/>
       <c r="AM74" s="5" t="n"/>
-      <c r="AP74" s="5" t="n"/>
+      <c r="AP74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -14760,7 +14770,7 @@
       <c r="AJ75" s="5" t="n"/>
       <c r="AK75" s="5" t="n"/>
       <c r="AM75" s="5" t="n"/>
-      <c r="AP75" s="5" t="n"/>
+      <c r="AP75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
@@ -14771,7 +14781,7 @@
       <c r="AJ76" s="5" t="n"/>
       <c r="AK76" s="5" t="n"/>
       <c r="AM76" s="5" t="n"/>
-      <c r="AP76" s="5" t="n"/>
+      <c r="AP76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n"/>
@@ -14782,7 +14792,7 @@
       <c r="AJ77" s="5" t="n"/>
       <c r="AK77" s="5" t="n"/>
       <c r="AM77" s="5" t="n"/>
-      <c r="AP77" s="5" t="n"/>
+      <c r="AP77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -14793,7 +14803,7 @@
       <c r="AJ78" s="5" t="n"/>
       <c r="AK78" s="5" t="n"/>
       <c r="AM78" s="5" t="n"/>
-      <c r="AP78" s="5" t="n"/>
+      <c r="AP78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -14804,7 +14814,7 @@
       <c r="AJ79" s="5" t="n"/>
       <c r="AK79" s="5" t="n"/>
       <c r="AM79" s="5" t="n"/>
-      <c r="AP79" s="5" t="n"/>
+      <c r="AP79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
@@ -14815,7 +14825,7 @@
       <c r="AJ80" s="5" t="n"/>
       <c r="AK80" s="5" t="n"/>
       <c r="AM80" s="5" t="n"/>
-      <c r="AP80" s="5" t="n"/>
+      <c r="AP80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
@@ -14826,7 +14836,7 @@
       <c r="AJ81" s="5" t="n"/>
       <c r="AK81" s="5" t="n"/>
       <c r="AM81" s="5" t="n"/>
-      <c r="AP81" s="5" t="n"/>
+      <c r="AP81" s="6" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -14837,7 +14847,7 @@
       <c r="AJ82" s="5" t="n"/>
       <c r="AK82" s="5" t="n"/>
       <c r="AM82" s="5" t="n"/>
-      <c r="AP82" s="5" t="n"/>
+      <c r="AP82" s="6" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -14848,7 +14858,7 @@
       <c r="AJ83" s="5" t="n"/>
       <c r="AK83" s="5" t="n"/>
       <c r="AM83" s="5" t="n"/>
-      <c r="AP83" s="5" t="n"/>
+      <c r="AP83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n"/>
@@ -14859,7 +14869,7 @@
       <c r="AJ84" s="5" t="n"/>
       <c r="AK84" s="5" t="n"/>
       <c r="AM84" s="5" t="n"/>
-      <c r="AP84" s="5" t="n"/>
+      <c r="AP84" s="6" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
@@ -14870,7 +14880,7 @@
       <c r="AJ85" s="5" t="n"/>
       <c r="AK85" s="5" t="n"/>
       <c r="AM85" s="5" t="n"/>
-      <c r="AP85" s="5" t="n"/>
+      <c r="AP85" s="6" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n"/>
@@ -14881,7 +14891,7 @@
       <c r="AJ86" s="5" t="n"/>
       <c r="AK86" s="5" t="n"/>
       <c r="AM86" s="5" t="n"/>
-      <c r="AP86" s="5" t="n"/>
+      <c r="AP86" s="6" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n"/>
@@ -14892,7 +14902,7 @@
       <c r="AJ87" s="5" t="n"/>
       <c r="AK87" s="5" t="n"/>
       <c r="AM87" s="5" t="n"/>
-      <c r="AP87" s="5" t="n"/>
+      <c r="AP87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n"/>
@@ -14903,7 +14913,7 @@
       <c r="AJ88" s="5" t="n"/>
       <c r="AK88" s="5" t="n"/>
       <c r="AM88" s="5" t="n"/>
-      <c r="AP88" s="5" t="n"/>
+      <c r="AP88" s="6" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n"/>
@@ -14914,7 +14924,7 @@
       <c r="AJ89" s="5" t="n"/>
       <c r="AK89" s="5" t="n"/>
       <c r="AM89" s="5" t="n"/>
-      <c r="AP89" s="5" t="n"/>
+      <c r="AP89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n"/>
@@ -14925,7 +14935,7 @@
       <c r="AJ90" s="5" t="n"/>
       <c r="AK90" s="5" t="n"/>
       <c r="AM90" s="5" t="n"/>
-      <c r="AP90" s="5" t="n"/>
+      <c r="AP90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n"/>
@@ -14936,7 +14946,7 @@
       <c r="AJ91" s="5" t="n"/>
       <c r="AK91" s="5" t="n"/>
       <c r="AM91" s="5" t="n"/>
-      <c r="AP91" s="5" t="n"/>
+      <c r="AP91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n"/>
@@ -14947,7 +14957,7 @@
       <c r="AJ92" s="5" t="n"/>
       <c r="AK92" s="5" t="n"/>
       <c r="AM92" s="5" t="n"/>
-      <c r="AP92" s="5" t="n"/>
+      <c r="AP92" s="6" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
@@ -14958,7 +14968,7 @@
       <c r="AJ93" s="5" t="n"/>
       <c r="AK93" s="5" t="n"/>
       <c r="AM93" s="5" t="n"/>
-      <c r="AP93" s="5" t="n"/>
+      <c r="AP93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n"/>
@@ -14969,7 +14979,7 @@
       <c r="AJ94" s="5" t="n"/>
       <c r="AK94" s="5" t="n"/>
       <c r="AM94" s="5" t="n"/>
-      <c r="AP94" s="5" t="n"/>
+      <c r="AP94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n"/>
@@ -14980,7 +14990,7 @@
       <c r="AJ95" s="5" t="n"/>
       <c r="AK95" s="5" t="n"/>
       <c r="AM95" s="5" t="n"/>
-      <c r="AP95" s="5" t="n"/>
+      <c r="AP95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
@@ -14991,7 +15001,7 @@
       <c r="AJ96" s="5" t="n"/>
       <c r="AK96" s="5" t="n"/>
       <c r="AM96" s="5" t="n"/>
-      <c r="AP96" s="5" t="n"/>
+      <c r="AP96" s="6" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n"/>
@@ -15002,7 +15012,7 @@
       <c r="AJ97" s="5" t="n"/>
       <c r="AK97" s="5" t="n"/>
       <c r="AM97" s="5" t="n"/>
-      <c r="AP97" s="5" t="n"/>
+      <c r="AP97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n"/>
@@ -15013,7 +15023,7 @@
       <c r="AJ98" s="5" t="n"/>
       <c r="AK98" s="5" t="n"/>
       <c r="AM98" s="5" t="n"/>
-      <c r="AP98" s="5" t="n"/>
+      <c r="AP98" s="6" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n"/>
@@ -15024,7 +15034,7 @@
       <c r="AJ99" s="5" t="n"/>
       <c r="AK99" s="5" t="n"/>
       <c r="AM99" s="5" t="n"/>
-      <c r="AP99" s="5" t="n"/>
+      <c r="AP99" s="6" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n"/>
@@ -15035,7 +15045,7 @@
       <c r="AJ100" s="5" t="n"/>
       <c r="AK100" s="5" t="n"/>
       <c r="AM100" s="5" t="n"/>
-      <c r="AP100" s="5" t="n"/>
+      <c r="AP100" s="6" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n"/>
@@ -15046,7 +15056,7 @@
       <c r="AJ101" s="5" t="n"/>
       <c r="AK101" s="5" t="n"/>
       <c r="AM101" s="5" t="n"/>
-      <c r="AP101" s="5" t="n"/>
+      <c r="AP101" s="6" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n"/>
@@ -15057,7 +15067,7 @@
       <c r="AJ102" s="5" t="n"/>
       <c r="AK102" s="5" t="n"/>
       <c r="AM102" s="5" t="n"/>
-      <c r="AP102" s="5" t="n"/>
+      <c r="AP102" s="6" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n"/>
@@ -15068,7 +15078,7 @@
       <c r="AJ103" s="5" t="n"/>
       <c r="AK103" s="5" t="n"/>
       <c r="AM103" s="5" t="n"/>
-      <c r="AP103" s="5" t="n"/>
+      <c r="AP103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n"/>
@@ -15079,7 +15089,7 @@
       <c r="AJ104" s="5" t="n"/>
       <c r="AK104" s="5" t="n"/>
       <c r="AM104" s="5" t="n"/>
-      <c r="AP104" s="5" t="n"/>
+      <c r="AP104" s="6" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n"/>
@@ -15090,7 +15100,7 @@
       <c r="AJ105" s="5" t="n"/>
       <c r="AK105" s="5" t="n"/>
       <c r="AM105" s="5" t="n"/>
-      <c r="AP105" s="5" t="n"/>
+      <c r="AP105" s="6" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n"/>
@@ -15101,7 +15111,7 @@
       <c r="AJ106" s="5" t="n"/>
       <c r="AK106" s="5" t="n"/>
       <c r="AM106" s="5" t="n"/>
-      <c r="AP106" s="5" t="n"/>
+      <c r="AP106" s="6" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
@@ -15112,7 +15122,7 @@
       <c r="AJ107" s="5" t="n"/>
       <c r="AK107" s="5" t="n"/>
       <c r="AM107" s="5" t="n"/>
-      <c r="AP107" s="5" t="n"/>
+      <c r="AP107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n"/>
@@ -15123,7 +15133,7 @@
       <c r="AJ108" s="5" t="n"/>
       <c r="AK108" s="5" t="n"/>
       <c r="AM108" s="5" t="n"/>
-      <c r="AP108" s="5" t="n"/>
+      <c r="AP108" s="6" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n"/>
@@ -15134,7 +15144,7 @@
       <c r="AJ109" s="5" t="n"/>
       <c r="AK109" s="5" t="n"/>
       <c r="AM109" s="5" t="n"/>
-      <c r="AP109" s="5" t="n"/>
+      <c r="AP109" s="6" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n"/>
@@ -15145,7 +15155,7 @@
       <c r="AJ110" s="5" t="n"/>
       <c r="AK110" s="5" t="n"/>
       <c r="AM110" s="5" t="n"/>
-      <c r="AP110" s="5" t="n"/>
+      <c r="AP110" s="6" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n"/>
@@ -15156,7 +15166,7 @@
       <c r="AJ111" s="5" t="n"/>
       <c r="AK111" s="5" t="n"/>
       <c r="AM111" s="5" t="n"/>
-      <c r="AP111" s="5" t="n"/>
+      <c r="AP111" s="6" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n"/>
@@ -15167,7 +15177,7 @@
       <c r="AJ112" s="5" t="n"/>
       <c r="AK112" s="5" t="n"/>
       <c r="AM112" s="5" t="n"/>
-      <c r="AP112" s="5" t="n"/>
+      <c r="AP112" s="6" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n"/>
@@ -15178,7 +15188,7 @@
       <c r="AJ113" s="5" t="n"/>
       <c r="AK113" s="5" t="n"/>
       <c r="AM113" s="5" t="n"/>
-      <c r="AP113" s="5" t="n"/>
+      <c r="AP113" s="6" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n"/>
@@ -15189,7 +15199,7 @@
       <c r="AJ114" s="5" t="n"/>
       <c r="AK114" s="5" t="n"/>
       <c r="AM114" s="5" t="n"/>
-      <c r="AP114" s="5" t="n"/>
+      <c r="AP114" s="6" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n"/>
@@ -15200,7 +15210,7 @@
       <c r="AJ115" s="5" t="n"/>
       <c r="AK115" s="5" t="n"/>
       <c r="AM115" s="5" t="n"/>
-      <c r="AP115" s="5" t="n"/>
+      <c r="AP115" s="6" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n"/>
@@ -15211,7 +15221,7 @@
       <c r="AJ116" s="5" t="n"/>
       <c r="AK116" s="5" t="n"/>
       <c r="AM116" s="5" t="n"/>
-      <c r="AP116" s="5" t="n"/>
+      <c r="AP116" s="6" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n"/>
@@ -15222,7 +15232,7 @@
       <c r="AJ117" s="5" t="n"/>
       <c r="AK117" s="5" t="n"/>
       <c r="AM117" s="5" t="n"/>
-      <c r="AP117" s="5" t="n"/>
+      <c r="AP117" s="6" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n"/>
@@ -15233,7 +15243,7 @@
       <c r="AJ118" s="5" t="n"/>
       <c r="AK118" s="5" t="n"/>
       <c r="AM118" s="5" t="n"/>
-      <c r="AP118" s="5" t="n"/>
+      <c r="AP118" s="6" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n"/>
@@ -15244,7 +15254,7 @@
       <c r="AJ119" s="5" t="n"/>
       <c r="AK119" s="5" t="n"/>
       <c r="AM119" s="5" t="n"/>
-      <c r="AP119" s="5" t="n"/>
+      <c r="AP119" s="6" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n"/>
@@ -15255,7 +15265,7 @@
       <c r="AJ120" s="5" t="n"/>
       <c r="AK120" s="5" t="n"/>
       <c r="AM120" s="5" t="n"/>
-      <c r="AP120" s="5" t="n"/>
+      <c r="AP120" s="6" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n"/>
@@ -15266,7 +15276,7 @@
       <c r="AJ121" s="5" t="n"/>
       <c r="AK121" s="5" t="n"/>
       <c r="AM121" s="5" t="n"/>
-      <c r="AP121" s="5" t="n"/>
+      <c r="AP121" s="6" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n"/>
@@ -15277,7 +15287,7 @@
       <c r="AJ122" s="5" t="n"/>
       <c r="AK122" s="5" t="n"/>
       <c r="AM122" s="5" t="n"/>
-      <c r="AP122" s="5" t="n"/>
+      <c r="AP122" s="6" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n"/>
@@ -15288,7 +15298,7 @@
       <c r="AJ123" s="5" t="n"/>
       <c r="AK123" s="5" t="n"/>
       <c r="AM123" s="5" t="n"/>
-      <c r="AP123" s="5" t="n"/>
+      <c r="AP123" s="6" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n"/>
@@ -15299,7 +15309,7 @@
       <c r="AJ124" s="5" t="n"/>
       <c r="AK124" s="5" t="n"/>
       <c r="AM124" s="5" t="n"/>
-      <c r="AP124" s="5" t="n"/>
+      <c r="AP124" s="6" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n"/>
@@ -15310,7 +15320,7 @@
       <c r="AJ125" s="5" t="n"/>
       <c r="AK125" s="5" t="n"/>
       <c r="AM125" s="5" t="n"/>
-      <c r="AP125" s="5" t="n"/>
+      <c r="AP125" s="6" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n"/>
@@ -15321,7 +15331,7 @@
       <c r="AJ126" s="5" t="n"/>
       <c r="AK126" s="5" t="n"/>
       <c r="AM126" s="5" t="n"/>
-      <c r="AP126" s="5" t="n"/>
+      <c r="AP126" s="6" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n"/>
@@ -15332,7 +15342,7 @@
       <c r="AJ127" s="5" t="n"/>
       <c r="AK127" s="5" t="n"/>
       <c r="AM127" s="5" t="n"/>
-      <c r="AP127" s="5" t="n"/>
+      <c r="AP127" s="6" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n"/>
@@ -15343,7 +15353,7 @@
       <c r="AJ128" s="5" t="n"/>
       <c r="AK128" s="5" t="n"/>
       <c r="AM128" s="5" t="n"/>
-      <c r="AP128" s="5" t="n"/>
+      <c r="AP128" s="6" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n"/>
@@ -15354,7 +15364,7 @@
       <c r="AJ129" s="5" t="n"/>
       <c r="AK129" s="5" t="n"/>
       <c r="AM129" s="5" t="n"/>
-      <c r="AP129" s="5" t="n"/>
+      <c r="AP129" s="6" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n"/>
@@ -15365,7 +15375,7 @@
       <c r="AJ130" s="5" t="n"/>
       <c r="AK130" s="5" t="n"/>
       <c r="AM130" s="5" t="n"/>
-      <c r="AP130" s="5" t="n"/>
+      <c r="AP130" s="6" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n"/>
@@ -15376,7 +15386,7 @@
       <c r="AJ131" s="5" t="n"/>
       <c r="AK131" s="5" t="n"/>
       <c r="AM131" s="5" t="n"/>
-      <c r="AP131" s="5" t="n"/>
+      <c r="AP131" s="6" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n"/>
@@ -15387,7 +15397,7 @@
       <c r="AJ132" s="5" t="n"/>
       <c r="AK132" s="5" t="n"/>
       <c r="AM132" s="5" t="n"/>
-      <c r="AP132" s="5" t="n"/>
+      <c r="AP132" s="6" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n"/>
@@ -15398,7 +15408,7 @@
       <c r="AJ133" s="5" t="n"/>
       <c r="AK133" s="5" t="n"/>
       <c r="AM133" s="5" t="n"/>
-      <c r="AP133" s="5" t="n"/>
+      <c r="AP133" s="6" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n"/>
@@ -15409,7 +15419,7 @@
       <c r="AJ134" s="5" t="n"/>
       <c r="AK134" s="5" t="n"/>
       <c r="AM134" s="5" t="n"/>
-      <c r="AP134" s="5" t="n"/>
+      <c r="AP134" s="6" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n"/>
@@ -15420,7 +15430,7 @@
       <c r="AJ135" s="5" t="n"/>
       <c r="AK135" s="5" t="n"/>
       <c r="AM135" s="5" t="n"/>
-      <c r="AP135" s="5" t="n"/>
+      <c r="AP135" s="6" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n"/>
@@ -15431,7 +15441,7 @@
       <c r="AJ136" s="5" t="n"/>
       <c r="AK136" s="5" t="n"/>
       <c r="AM136" s="5" t="n"/>
-      <c r="AP136" s="5" t="n"/>
+      <c r="AP136" s="6" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n"/>
@@ -15442,7 +15452,7 @@
       <c r="AJ137" s="5" t="n"/>
       <c r="AK137" s="5" t="n"/>
       <c r="AM137" s="5" t="n"/>
-      <c r="AP137" s="5" t="n"/>
+      <c r="AP137" s="6" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n"/>
@@ -15453,7 +15463,7 @@
       <c r="AJ138" s="5" t="n"/>
       <c r="AK138" s="5" t="n"/>
       <c r="AM138" s="5" t="n"/>
-      <c r="AP138" s="5" t="n"/>
+      <c r="AP138" s="6" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n"/>
@@ -15464,7 +15474,7 @@
       <c r="AJ139" s="5" t="n"/>
       <c r="AK139" s="5" t="n"/>
       <c r="AM139" s="5" t="n"/>
-      <c r="AP139" s="5" t="n"/>
+      <c r="AP139" s="6" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n"/>
@@ -15475,7 +15485,7 @@
       <c r="AJ140" s="5" t="n"/>
       <c r="AK140" s="5" t="n"/>
       <c r="AM140" s="5" t="n"/>
-      <c r="AP140" s="5" t="n"/>
+      <c r="AP140" s="6" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n"/>
@@ -15486,7 +15496,7 @@
       <c r="AJ141" s="5" t="n"/>
       <c r="AK141" s="5" t="n"/>
       <c r="AM141" s="5" t="n"/>
-      <c r="AP141" s="5" t="n"/>
+      <c r="AP141" s="6" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n"/>
@@ -15497,7 +15507,7 @@
       <c r="AJ142" s="5" t="n"/>
       <c r="AK142" s="5" t="n"/>
       <c r="AM142" s="5" t="n"/>
-      <c r="AP142" s="5" t="n"/>
+      <c r="AP142" s="6" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n"/>
@@ -15508,7 +15518,7 @@
       <c r="AJ143" s="5" t="n"/>
       <c r="AK143" s="5" t="n"/>
       <c r="AM143" s="5" t="n"/>
-      <c r="AP143" s="5" t="n"/>
+      <c r="AP143" s="6" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n"/>
@@ -15519,7 +15529,7 @@
       <c r="AJ144" s="5" t="n"/>
       <c r="AK144" s="5" t="n"/>
       <c r="AM144" s="5" t="n"/>
-      <c r="AP144" s="5" t="n"/>
+      <c r="AP144" s="6" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n"/>
@@ -15530,7 +15540,7 @@
       <c r="AJ145" s="5" t="n"/>
       <c r="AK145" s="5" t="n"/>
       <c r="AM145" s="5" t="n"/>
-      <c r="AP145" s="5" t="n"/>
+      <c r="AP145" s="6" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n"/>
@@ -15541,7 +15551,7 @@
       <c r="AJ146" s="5" t="n"/>
       <c r="AK146" s="5" t="n"/>
       <c r="AM146" s="5" t="n"/>
-      <c r="AP146" s="5" t="n"/>
+      <c r="AP146" s="6" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n"/>
@@ -15552,7 +15562,7 @@
       <c r="AJ147" s="5" t="n"/>
       <c r="AK147" s="5" t="n"/>
       <c r="AM147" s="5" t="n"/>
-      <c r="AP147" s="5" t="n"/>
+      <c r="AP147" s="6" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n"/>
@@ -15563,7 +15573,7 @@
       <c r="AJ148" s="5" t="n"/>
       <c r="AK148" s="5" t="n"/>
       <c r="AM148" s="5" t="n"/>
-      <c r="AP148" s="5" t="n"/>
+      <c r="AP148" s="6" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n"/>
@@ -15574,7 +15584,7 @@
       <c r="AJ149" s="5" t="n"/>
       <c r="AK149" s="5" t="n"/>
       <c r="AM149" s="5" t="n"/>
-      <c r="AP149" s="5" t="n"/>
+      <c r="AP149" s="6" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n"/>
@@ -15585,7 +15595,7 @@
       <c r="AJ150" s="5" t="n"/>
       <c r="AK150" s="5" t="n"/>
       <c r="AM150" s="5" t="n"/>
-      <c r="AP150" s="5" t="n"/>
+      <c r="AP150" s="6" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n"/>
@@ -15596,7 +15606,7 @@
       <c r="AJ151" s="5" t="n"/>
       <c r="AK151" s="5" t="n"/>
       <c r="AM151" s="5" t="n"/>
-      <c r="AP151" s="5" t="n"/>
+      <c r="AP151" s="6" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n"/>
@@ -15607,7 +15617,7 @@
       <c r="AJ152" s="5" t="n"/>
       <c r="AK152" s="5" t="n"/>
       <c r="AM152" s="5" t="n"/>
-      <c r="AP152" s="5" t="n"/>
+      <c r="AP152" s="6" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n"/>
@@ -15618,7 +15628,7 @@
       <c r="AJ153" s="5" t="n"/>
       <c r="AK153" s="5" t="n"/>
       <c r="AM153" s="5" t="n"/>
-      <c r="AP153" s="5" t="n"/>
+      <c r="AP153" s="6" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n"/>
@@ -15629,7 +15639,7 @@
       <c r="AJ154" s="5" t="n"/>
       <c r="AK154" s="5" t="n"/>
       <c r="AM154" s="5" t="n"/>
-      <c r="AP154" s="5" t="n"/>
+      <c r="AP154" s="6" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n"/>
@@ -15640,7 +15650,7 @@
       <c r="AJ155" s="5" t="n"/>
       <c r="AK155" s="5" t="n"/>
       <c r="AM155" s="5" t="n"/>
-      <c r="AP155" s="5" t="n"/>
+      <c r="AP155" s="6" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n"/>
@@ -15651,7 +15661,7 @@
       <c r="AJ156" s="5" t="n"/>
       <c r="AK156" s="5" t="n"/>
       <c r="AM156" s="5" t="n"/>
-      <c r="AP156" s="5" t="n"/>
+      <c r="AP156" s="6" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n"/>
@@ -15662,7 +15672,7 @@
       <c r="AJ157" s="5" t="n"/>
       <c r="AK157" s="5" t="n"/>
       <c r="AM157" s="5" t="n"/>
-      <c r="AP157" s="5" t="n"/>
+      <c r="AP157" s="6" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n"/>
@@ -15673,7 +15683,7 @@
       <c r="AJ158" s="5" t="n"/>
       <c r="AK158" s="5" t="n"/>
       <c r="AM158" s="5" t="n"/>
-      <c r="AP158" s="5" t="n"/>
+      <c r="AP158" s="6" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n"/>
@@ -15684,7 +15694,7 @@
       <c r="AJ159" s="5" t="n"/>
       <c r="AK159" s="5" t="n"/>
       <c r="AM159" s="5" t="n"/>
-      <c r="AP159" s="5" t="n"/>
+      <c r="AP159" s="6" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n"/>
@@ -15695,7 +15705,7 @@
       <c r="AJ160" s="5" t="n"/>
       <c r="AK160" s="5" t="n"/>
       <c r="AM160" s="5" t="n"/>
-      <c r="AP160" s="5" t="n"/>
+      <c r="AP160" s="6" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n"/>
@@ -15706,7 +15716,7 @@
       <c r="AJ161" s="5" t="n"/>
       <c r="AK161" s="5" t="n"/>
       <c r="AM161" s="5" t="n"/>
-      <c r="AP161" s="5" t="n"/>
+      <c r="AP161" s="6" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n"/>
@@ -15717,7 +15727,7 @@
       <c r="AJ162" s="5" t="n"/>
       <c r="AK162" s="5" t="n"/>
       <c r="AM162" s="5" t="n"/>
-      <c r="AP162" s="5" t="n"/>
+      <c r="AP162" s="6" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n"/>
@@ -15728,7 +15738,7 @@
       <c r="AJ163" s="5" t="n"/>
       <c r="AK163" s="5" t="n"/>
       <c r="AM163" s="5" t="n"/>
-      <c r="AP163" s="5" t="n"/>
+      <c r="AP163" s="6" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n"/>
@@ -15739,7 +15749,7 @@
       <c r="AJ164" s="5" t="n"/>
       <c r="AK164" s="5" t="n"/>
       <c r="AM164" s="5" t="n"/>
-      <c r="AP164" s="5" t="n"/>
+      <c r="AP164" s="6" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n"/>
@@ -15750,7 +15760,7 @@
       <c r="AJ165" s="5" t="n"/>
       <c r="AK165" s="5" t="n"/>
       <c r="AM165" s="5" t="n"/>
-      <c r="AP165" s="5" t="n"/>
+      <c r="AP165" s="6" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n"/>
@@ -15761,7 +15771,7 @@
       <c r="AJ166" s="5" t="n"/>
       <c r="AK166" s="5" t="n"/>
       <c r="AM166" s="5" t="n"/>
-      <c r="AP166" s="5" t="n"/>
+      <c r="AP166" s="6" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n"/>
@@ -15772,7 +15782,7 @@
       <c r="AJ167" s="5" t="n"/>
       <c r="AK167" s="5" t="n"/>
       <c r="AM167" s="5" t="n"/>
-      <c r="AP167" s="5" t="n"/>
+      <c r="AP167" s="6" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n"/>
@@ -15783,7 +15793,7 @@
       <c r="AJ168" s="5" t="n"/>
       <c r="AK168" s="5" t="n"/>
       <c r="AM168" s="5" t="n"/>
-      <c r="AP168" s="5" t="n"/>
+      <c r="AP168" s="6" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n"/>
@@ -15794,7 +15804,7 @@
       <c r="AJ169" s="5" t="n"/>
       <c r="AK169" s="5" t="n"/>
       <c r="AM169" s="5" t="n"/>
-      <c r="AP169" s="5" t="n"/>
+      <c r="AP169" s="6" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n"/>
@@ -15805,7 +15815,7 @@
       <c r="AJ170" s="5" t="n"/>
       <c r="AK170" s="5" t="n"/>
       <c r="AM170" s="5" t="n"/>
-      <c r="AP170" s="5" t="n"/>
+      <c r="AP170" s="6" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="n"/>
@@ -15816,7 +15826,7 @@
       <c r="AJ171" s="5" t="n"/>
       <c r="AK171" s="5" t="n"/>
       <c r="AM171" s="5" t="n"/>
-      <c r="AP171" s="5" t="n"/>
+      <c r="AP171" s="6" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n"/>
@@ -15827,7 +15837,7 @@
       <c r="AJ172" s="5" t="n"/>
       <c r="AK172" s="5" t="n"/>
       <c r="AM172" s="5" t="n"/>
-      <c r="AP172" s="5" t="n"/>
+      <c r="AP172" s="6" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="n"/>
@@ -15838,7 +15848,7 @@
       <c r="AJ173" s="5" t="n"/>
       <c r="AK173" s="5" t="n"/>
       <c r="AM173" s="5" t="n"/>
-      <c r="AP173" s="5" t="n"/>
+      <c r="AP173" s="6" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n"/>
@@ -15849,7 +15859,7 @@
       <c r="AJ174" s="5" t="n"/>
       <c r="AK174" s="5" t="n"/>
       <c r="AM174" s="5" t="n"/>
-      <c r="AP174" s="5" t="n"/>
+      <c r="AP174" s="6" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n"/>
@@ -15860,7 +15870,7 @@
       <c r="AJ175" s="5" t="n"/>
       <c r="AK175" s="5" t="n"/>
       <c r="AM175" s="5" t="n"/>
-      <c r="AP175" s="5" t="n"/>
+      <c r="AP175" s="6" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n"/>
@@ -15871,7 +15881,7 @@
       <c r="AJ176" s="5" t="n"/>
       <c r="AK176" s="5" t="n"/>
       <c r="AM176" s="5" t="n"/>
-      <c r="AP176" s="5" t="n"/>
+      <c r="AP176" s="6" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n"/>
@@ -15882,7 +15892,7 @@
       <c r="AJ177" s="5" t="n"/>
       <c r="AK177" s="5" t="n"/>
       <c r="AM177" s="5" t="n"/>
-      <c r="AP177" s="5" t="n"/>
+      <c r="AP177" s="6" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="5" t="n"/>
@@ -15893,7 +15903,7 @@
       <c r="AJ178" s="5" t="n"/>
       <c r="AK178" s="5" t="n"/>
       <c r="AM178" s="5" t="n"/>
-      <c r="AP178" s="5" t="n"/>
+      <c r="AP178" s="6" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n"/>
@@ -15904,7 +15914,7 @@
       <c r="AJ179" s="5" t="n"/>
       <c r="AK179" s="5" t="n"/>
       <c r="AM179" s="5" t="n"/>
-      <c r="AP179" s="5" t="n"/>
+      <c r="AP179" s="6" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n"/>
@@ -15915,7 +15925,7 @@
       <c r="AJ180" s="5" t="n"/>
       <c r="AK180" s="5" t="n"/>
       <c r="AM180" s="5" t="n"/>
-      <c r="AP180" s="5" t="n"/>
+      <c r="AP180" s="6" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n"/>
@@ -15926,7 +15936,7 @@
       <c r="AJ181" s="5" t="n"/>
       <c r="AK181" s="5" t="n"/>
       <c r="AM181" s="5" t="n"/>
-      <c r="AP181" s="5" t="n"/>
+      <c r="AP181" s="6" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n"/>
@@ -15937,7 +15947,7 @@
       <c r="AJ182" s="5" t="n"/>
       <c r="AK182" s="5" t="n"/>
       <c r="AM182" s="5" t="n"/>
-      <c r="AP182" s="5" t="n"/>
+      <c r="AP182" s="6" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
@@ -15948,7 +15958,7 @@
       <c r="AJ183" s="5" t="n"/>
       <c r="AK183" s="5" t="n"/>
       <c r="AM183" s="5" t="n"/>
-      <c r="AP183" s="5" t="n"/>
+      <c r="AP183" s="6" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
@@ -15959,7 +15969,7 @@
       <c r="AJ184" s="5" t="n"/>
       <c r="AK184" s="5" t="n"/>
       <c r="AM184" s="5" t="n"/>
-      <c r="AP184" s="5" t="n"/>
+      <c r="AP184" s="6" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n"/>
@@ -15970,7 +15980,7 @@
       <c r="AJ185" s="5" t="n"/>
       <c r="AK185" s="5" t="n"/>
       <c r="AM185" s="5" t="n"/>
-      <c r="AP185" s="5" t="n"/>
+      <c r="AP185" s="6" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n"/>
@@ -15981,7 +15991,7 @@
       <c r="AJ186" s="5" t="n"/>
       <c r="AK186" s="5" t="n"/>
       <c r="AM186" s="5" t="n"/>
-      <c r="AP186" s="5" t="n"/>
+      <c r="AP186" s="6" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="n"/>
@@ -15992,7 +16002,7 @@
       <c r="AJ187" s="5" t="n"/>
       <c r="AK187" s="5" t="n"/>
       <c r="AM187" s="5" t="n"/>
-      <c r="AP187" s="5" t="n"/>
+      <c r="AP187" s="6" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n"/>
@@ -16003,7 +16013,7 @@
       <c r="AJ188" s="5" t="n"/>
       <c r="AK188" s="5" t="n"/>
       <c r="AM188" s="5" t="n"/>
-      <c r="AP188" s="5" t="n"/>
+      <c r="AP188" s="6" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n"/>
@@ -16014,7 +16024,7 @@
       <c r="AJ189" s="5" t="n"/>
       <c r="AK189" s="5" t="n"/>
       <c r="AM189" s="5" t="n"/>
-      <c r="AP189" s="5" t="n"/>
+      <c r="AP189" s="6" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n"/>
@@ -16025,7 +16035,7 @@
       <c r="AJ190" s="5" t="n"/>
       <c r="AK190" s="5" t="n"/>
       <c r="AM190" s="5" t="n"/>
-      <c r="AP190" s="5" t="n"/>
+      <c r="AP190" s="6" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="n"/>
@@ -16036,7 +16046,7 @@
       <c r="AJ191" s="5" t="n"/>
       <c r="AK191" s="5" t="n"/>
       <c r="AM191" s="5" t="n"/>
-      <c r="AP191" s="5" t="n"/>
+      <c r="AP191" s="6" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="n"/>
@@ -16047,7 +16057,7 @@
       <c r="AJ192" s="5" t="n"/>
       <c r="AK192" s="5" t="n"/>
       <c r="AM192" s="5" t="n"/>
-      <c r="AP192" s="5" t="n"/>
+      <c r="AP192" s="6" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n"/>
@@ -16058,7 +16068,7 @@
       <c r="AJ193" s="5" t="n"/>
       <c r="AK193" s="5" t="n"/>
       <c r="AM193" s="5" t="n"/>
-      <c r="AP193" s="5" t="n"/>
+      <c r="AP193" s="6" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n"/>
@@ -16069,7 +16079,7 @@
       <c r="AJ194" s="5" t="n"/>
       <c r="AK194" s="5" t="n"/>
       <c r="AM194" s="5" t="n"/>
-      <c r="AP194" s="5" t="n"/>
+      <c r="AP194" s="6" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="n"/>
@@ -16080,7 +16090,7 @@
       <c r="AJ195" s="5" t="n"/>
       <c r="AK195" s="5" t="n"/>
       <c r="AM195" s="5" t="n"/>
-      <c r="AP195" s="5" t="n"/>
+      <c r="AP195" s="6" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n"/>
@@ -16091,7 +16101,7 @@
       <c r="AJ196" s="5" t="n"/>
       <c r="AK196" s="5" t="n"/>
       <c r="AM196" s="5" t="n"/>
-      <c r="AP196" s="5" t="n"/>
+      <c r="AP196" s="6" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="n"/>
@@ -16102,7 +16112,7 @@
       <c r="AJ197" s="5" t="n"/>
       <c r="AK197" s="5" t="n"/>
       <c r="AM197" s="5" t="n"/>
-      <c r="AP197" s="5" t="n"/>
+      <c r="AP197" s="6" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="n"/>
@@ -16113,7 +16123,7 @@
       <c r="AJ198" s="5" t="n"/>
       <c r="AK198" s="5" t="n"/>
       <c r="AM198" s="5" t="n"/>
-      <c r="AP198" s="5" t="n"/>
+      <c r="AP198" s="6" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n"/>
@@ -16124,7 +16134,7 @@
       <c r="AJ199" s="5" t="n"/>
       <c r="AK199" s="5" t="n"/>
       <c r="AM199" s="5" t="n"/>
-      <c r="AP199" s="5" t="n"/>
+      <c r="AP199" s="6" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n"/>
@@ -16135,7 +16145,7 @@
       <c r="AJ200" s="5" t="n"/>
       <c r="AK200" s="5" t="n"/>
       <c r="AM200" s="5" t="n"/>
-      <c r="AP200" s="5" t="n"/>
+      <c r="AP200" s="6" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="5" t="n"/>
@@ -16146,7 +16156,7 @@
       <c r="AJ201" s="5" t="n"/>
       <c r="AK201" s="5" t="n"/>
       <c r="AM201" s="5" t="n"/>
-      <c r="AP201" s="5" t="n"/>
+      <c r="AP201" s="6" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="n"/>
@@ -16157,7 +16167,7 @@
       <c r="AJ202" s="5" t="n"/>
       <c r="AK202" s="5" t="n"/>
       <c r="AM202" s="5" t="n"/>
-      <c r="AP202" s="5" t="n"/>
+      <c r="AP202" s="6" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="n"/>
@@ -16168,7 +16178,7 @@
       <c r="AJ203" s="5" t="n"/>
       <c r="AK203" s="5" t="n"/>
       <c r="AM203" s="5" t="n"/>
-      <c r="AP203" s="5" t="n"/>
+      <c r="AP203" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -17299,8 +17309,7 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Consignar la edad del adolescente a la fecha del ingreso al dispositivo.
-Formato de fecha: dd/mm/aaaa.</t>
+          <t>Consignar la edad del adolescente a la fecha del ingreso al dispositivo.</t>
         </is>
       </c>
     </row>
@@ -19872,7 +19881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20154,12 +20163,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nombre del dispositivo</t>
+          <t>Hora de egreso del dispositivo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>dae_nombre_del_dispositivo_existe_en_archivo</t>
+          <t>mpj_dae_hora_de_egreso_del_dispositivo_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -20170,7 +20179,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -20194,12 +20203,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tipo de discapacidad</t>
+          <t>Fecha de egreso del dispositivo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>mpj_dae_tipo_de_discapacidad_obligatorio_si</t>
+          <t>mpj_dae_fecha_de_egreso_del_dispositivo_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -20230,16 +20239,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fecha de egreso del dispositivo</t>
+          <t>Hora de ingreso al dispositivo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>mpj_dae_fecha_de_egreso_del_dispositivo_comparar_valor</t>
+          <t>mpj_dae_hora_de_ingreso_al_dispositivo_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -20254,12 +20263,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Edad al ingreso</t>
+          <t>Fecha del relevamiento</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>mpj_dae_edad_al_ingreso_rango</t>
+          <t>mpj_dae_fecha_del_relevamiento_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -20270,16 +20279,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Edad al ingreso</t>
+          <t>Especificar destino al egreso</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>mpj_dae_edad_al_ingreso_rango</t>
+          <t>mpj_dae_especificar_destino_al_egreso_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -20294,12 +20303,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tipo de discapacidad</t>
+          <t>Hora de egreso del dispositivo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>mpj_dae_tipo_de_discapacidad_obligatorio_si</t>
+          <t>mpj_dae_hora_de_egreso_del_dispositivo_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -20310,16 +20319,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hora de ingreso al dispositivo</t>
+          <t>Fecha del relevamiento</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>mpj_dae_hora_de_ingreso_al_dispositivo_comparar_valor</t>
+          <t>mpj_dae_fecha_del_relevamiento_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -20334,30 +20343,10 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hora de ingreso al dispositivo</t>
+          <t>Fecha de egreso del dispositivo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
-        <is>
-          <t>mpj_dae_hora_de_ingreso_al_dispositivo_comparar_valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DAE</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>33</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Fecha de egreso del dispositivo</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
         <is>
           <t>mpj_dae_fecha_de_egreso_del_dispositivo_comparar_valor</t>
         </is>

--- a/runac/demo/MPJ_DAE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/runac/demo/MPJ_DAE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -1486,7 +1486,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>45676</v>
+        <v>45677</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>42.84</v>
       </c>
       <c r="AI4" s="5" t="n">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>45732</v>
+        <v>45733</v>
       </c>
       <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>24.05</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>32.15</v>
       </c>
       <c r="AI6" s="5" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>45800</v>
+        <v>45801</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>94.3</v>
       </c>
       <c r="AI7" s="5" t="n">
-        <v>45975</v>
+        <v>45976</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>45975</v>
+        <v>45976</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>45779</v>
+        <v>45780</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>80.87</v>
       </c>
       <c r="AI8" s="5" t="n">
-        <v>45841</v>
+        <v>45842</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>45841</v>
+        <v>45842</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>45782</v>
+        <v>45783</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45933</v>
+        <v>45934</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>59.26</v>
       </c>
       <c r="AI9" s="5" t="n">
-        <v>45935</v>
+        <v>45936</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>86.52</v>
       </c>
       <c r="AI10" s="5" t="n">
-        <v>45852</v>
+        <v>45853</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>45854</v>
+        <v>45855</v>
       </c>
       <c r="AL10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>1.21</v>
       </c>
       <c r="AI11" s="5" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2812,13 +2812,13 @@
         </is>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="AL11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>45602</v>
+        <v>45603</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45588</v>
+        <v>45589</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>25.38</v>
       </c>
       <c r="AI12" s="5" t="n">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2976,13 +2976,13 @@
         </is>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="AL12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>54.78</v>
       </c>
       <c r="AI13" s="5" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>77.34</v>
       </c>
       <c r="AI14" s="5" t="n">
-        <v>46010</v>
+        <v>46011</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>75.2</v>
       </c>
       <c r="AI15" s="5" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -3474,13 +3474,13 @@
         </is>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>45963</v>
+        <v>45964</v>
       </c>
       <c r="AL15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>45871</v>
+        <v>45872</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>28.63</v>
       </c>
       <c r="AI16" s="5" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>45730</v>
+        <v>45731</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>43.7</v>
       </c>
       <c r="AI17" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -3809,13 +3809,13 @@
         </is>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AL17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>45963</v>
+        <v>45964</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>45591</v>
+        <v>45592</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>3.42</v>
       </c>
       <c r="AI18" s="5" t="n">
-        <v>45654</v>
+        <v>45655</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3968,13 +3968,13 @@
         </is>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="AL18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45813</v>
+        <v>45814</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>45596</v>
+        <v>45597</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>95.05</v>
       </c>
       <c r="AI19" s="5" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>45781</v>
+        <v>45782</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45843</v>
+        <v>45844</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>16.13</v>
       </c>
       <c r="AI20" s="5" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -4308,13 +4308,13 @@
         </is>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="AL20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>45802</v>
+        <v>45803</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>34.28</v>
       </c>
       <c r="AI21" s="5" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -4476,13 +4476,13 @@
         </is>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="AL21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>45801</v>
+        <v>45802</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>45798</v>
+        <v>45799</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>99.98999999999999</v>
       </c>
       <c r="AI22" s="5" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -4644,13 +4644,13 @@
         </is>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="AL22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45612</v>
+        <v>45613</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>68.06</v>
       </c>
       <c r="AI23" s="5" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -4812,13 +4812,13 @@
         </is>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AL23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45836</v>
+        <v>45837</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>16.15</v>
       </c>
       <c r="AI24" s="5" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -4979,13 +4979,13 @@
         </is>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>46003</v>
+        <v>46004</v>
       </c>
       <c r="AL24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>88.15000000000001</v>
       </c>
       <c r="AI25" s="5" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -5143,13 +5143,13 @@
         </is>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="AL25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>35.83</v>
       </c>
       <c r="AI26" s="5" t="n">
-        <v>45853</v>
+        <v>45854</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -5311,13 +5311,13 @@
         </is>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="AL26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46082</v>
+        <v>46083</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>2.21</v>
       </c>
       <c r="AI27" s="5" t="n">
-        <v>45699</v>
+        <v>45700</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -5470,13 +5470,13 @@
         </is>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>45749</v>
+        <v>45750</v>
       </c>
       <c r="AL27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45975</v>
+        <v>45976</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>62.48</v>
       </c>
       <c r="AI28" s="5" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -5638,13 +5638,13 @@
         </is>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="AL28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>80.59</v>
       </c>
       <c r="AI29" s="5" t="n">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="AK29" s="5" t="n">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45949</v>
+        <v>45950</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>23.66</v>
       </c>
       <c r="AI30" s="5" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="AL30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>45798</v>
+        <v>45799</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>45814</v>
+        <v>45815</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>12.48</v>
       </c>
       <c r="AI31" s="5" t="n">
-        <v>46012</v>
+        <v>46013</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="AL31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45606</v>
+        <v>45607</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>55.67</v>
       </c>
       <c r="AI32" s="5" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -6294,13 +6294,13 @@
         </is>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="AL32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>59.11</v>
       </c>
       <c r="AI33" s="5" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="AD4" s="5" t="n">
-        <v>45829</v>
+        <v>45830</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="AJ4" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AK4" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="AM4" s="5" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>45872</v>
+        <v>45873</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -8853,10 +8853,10 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>45825</v>
+        <v>45826</v>
       </c>
       <c r="AD5" s="5" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -8884,10 +8884,10 @@
         </is>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="AM5" s="5" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="N6" s="5" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="O6" s="6" t="n">
         <v>10</v>
@@ -9039,10 +9039,10 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="AD6" s="5" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -9070,10 +9070,10 @@
         </is>
       </c>
       <c r="AJ6" s="5" t="n">
-        <v>45873</v>
+        <v>45874</v>
       </c>
       <c r="AK6" s="5" t="n">
-        <v>45906</v>
+        <v>45907</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="AM6" s="5" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>45700</v>
+        <v>45701</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>45828</v>
+        <v>45829</v>
       </c>
       <c r="AD7" s="5" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>45935</v>
+        <v>45936</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="AM7" s="5" t="n">
-        <v>45880</v>
+        <v>45881</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9429,10 +9429,10 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>45730</v>
+        <v>45731</v>
       </c>
       <c r="AD8" s="5" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -9460,10 +9460,10 @@
         </is>
       </c>
       <c r="AJ8" s="5" t="n">
-        <v>45894</v>
+        <v>45895</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="AM8" s="5" t="n">
-        <v>45903</v>
+        <v>45904</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9623,10 +9623,10 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45850</v>
+        <v>45851</v>
       </c>
       <c r="AD9" s="5" t="n">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="AJ9" s="5" t="n">
-        <v>45955</v>
+        <v>45956</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="AM9" s="5" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>45912</v>
+        <v>45913</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -9822,10 +9822,10 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45669</v>
+        <v>45670</v>
       </c>
       <c r="AD10" s="5" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -9853,10 +9853,10 @@
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>45698</v>
+        <v>45699</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="AM10" s="5" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45677</v>
+        <v>45678</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="AD11" s="5" t="n">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -10043,10 +10043,10 @@
         </is>
       </c>
       <c r="AJ11" s="5" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="AM11" s="5" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -10207,10 +10207,10 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45839</v>
+        <v>45840</v>
       </c>
       <c r="AD12" s="5" t="n">
-        <v>45817</v>
+        <v>45818</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -10238,10 +10238,10 @@
         </is>
       </c>
       <c r="AJ12" s="5" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="AK12" s="5" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         </is>
       </c>
       <c r="AM12" s="5" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -10402,10 +10402,10 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="AD13" s="5" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -10433,10 +10433,10 @@
         </is>
       </c>
       <c r="AJ13" s="5" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         </is>
       </c>
       <c r="AM13" s="5" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>45705</v>
+        <v>45706</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -10592,10 +10592,10 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="AD14" s="5" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -10623,10 +10623,10 @@
         </is>
       </c>
       <c r="AJ14" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AK14" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="AM14" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         </is>
       </c>
       <c r="N15" s="5" t="n">
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="O15" s="6" t="n">
         <v>8</v>
@@ -10782,10 +10782,10 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="AD15" s="5" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="AJ15" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AK15" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         </is>
       </c>
       <c r="AM15" s="5" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>45890</v>
+        <v>45891</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -10977,10 +10977,10 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>45947</v>
+        <v>45948</v>
       </c>
       <c r="AD16" s="5" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -11008,10 +11008,10 @@
         </is>
       </c>
       <c r="AJ16" s="5" t="n">
-        <v>46010</v>
+        <v>46011</v>
       </c>
       <c r="AK16" s="5" t="n">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         </is>
       </c>
       <c r="AM16" s="5" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -11172,10 +11172,10 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45774</v>
+        <v>45775</v>
       </c>
       <c r="AD17" s="5" t="n">
-        <v>45804</v>
+        <v>45805</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
-        <v>45792</v>
+        <v>45793</v>
       </c>
       <c r="AK17" s="5" t="n">
-        <v>45895</v>
+        <v>45896</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         </is>
       </c>
       <c r="AM17" s="5" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -11367,10 +11367,10 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>45792</v>
+        <v>45793</v>
       </c>
       <c r="AD18" s="5" t="n">
-        <v>45766</v>
+        <v>45767</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -11398,10 +11398,10 @@
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
-        <v>46384</v>
+        <v>46385</v>
       </c>
       <c r="AK18" s="5" t="n">
-        <v>45856</v>
+        <v>45857</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="AM18" s="5" t="n">
-        <v>45905</v>
+        <v>45906</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="AD19" s="5" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
-        <v>45853</v>
+        <v>45854</v>
       </c>
       <c r="AK19" s="5" t="n">
-        <v>45784</v>
+        <v>45785</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="AM19" s="5" t="n">
-        <v>45836</v>
+        <v>45837</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45894</v>
+        <v>45895</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -11747,10 +11747,10 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="AD20" s="5" t="n">
-        <v>45977</v>
+        <v>45978</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -11778,10 +11778,10 @@
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AK20" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AM20" s="5" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -11942,10 +11942,10 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="AD21" s="5" t="n">
-        <v>46367</v>
+        <v>46368</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -11973,10 +11973,10 @@
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AK21" s="5" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="AM21" s="5" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -12137,10 +12137,10 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="AD22" s="5" t="n">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -12168,10 +12168,10 @@
         </is>
       </c>
       <c r="AJ22" s="5" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="AK22" s="5" t="n">
-        <v>45940</v>
+        <v>45941</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="AM22" s="5" t="n">
-        <v>45935</v>
+        <v>45936</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -12328,10 +12328,10 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="AD23" s="5" t="n">
-        <v>46033</v>
+        <v>46034</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -12359,10 +12359,10 @@
         </is>
       </c>
       <c r="AJ23" s="5" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="AK23" s="5" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         </is>
       </c>
       <c r="AM23" s="5" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>46671</v>
+        <v>46672</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -12519,10 +12519,10 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="AD24" s="5" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -12550,10 +12550,10 @@
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AK24" s="5" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="AM24" s="5" t="n">
-        <v>46352</v>
+        <v>46353</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45608</v>
+        <v>45609</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -12714,10 +12714,10 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="AD25" s="5" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -12745,10 +12745,10 @@
         </is>
       </c>
       <c r="AJ25" s="5" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="AK25" s="5" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         </is>
       </c>
       <c r="AM25" s="5" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45904</v>
+        <v>45905</v>
       </c>
       <c r="AD26" s="5" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -12936,10 +12936,10 @@
         </is>
       </c>
       <c r="AJ26" s="5" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="AK26" s="5" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         </is>
       </c>
       <c r="AM26" s="5" t="n">
-        <v>46018</v>
+        <v>46019</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -13100,10 +13100,10 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>45817</v>
+        <v>45818</v>
       </c>
       <c r="AD27" s="5" t="n">
-        <v>46103</v>
+        <v>46104</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -13131,10 +13131,10 @@
         </is>
       </c>
       <c r="AJ27" s="5" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="AK27" s="5" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         </is>
       </c>
       <c r="AM27" s="5" t="n">
-        <v>45956</v>
+        <v>45957</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -13291,10 +13291,10 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45789</v>
+        <v>45790</v>
       </c>
       <c r="AD28" s="5" t="n">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="AJ28" s="5" t="n">
-        <v>45871</v>
+        <v>45872</v>
       </c>
       <c r="AK28" s="5" t="n">
-        <v>45954</v>
+        <v>45955</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         </is>
       </c>
       <c r="AM28" s="5" t="n">
-        <v>45905</v>
+        <v>45906</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -13482,41 +13482,41 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>45998</v>
+        <v>45999</v>
       </c>
       <c r="AD29" s="5" t="n">
+        <v>46152</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Prefectura</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Comisaría 1ª</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Cushamen</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Entre 12 y 24 hs</t>
+        </is>
+      </c>
+      <c r="AJ29" s="5" t="n">
         <v>46151</v>
       </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>Prefectura</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>Comisaría 1ª</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>Cushamen</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Entre 12 y 24 hs</t>
-        </is>
-      </c>
-      <c r="AJ29" s="5" t="n">
-        <v>46150</v>
-      </c>
       <c r="AK29" s="5" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         </is>
       </c>
       <c r="AM29" s="5" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -13676,10 +13676,10 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="AD30" s="5" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -13707,10 +13707,10 @@
         </is>
       </c>
       <c r="AJ30" s="5" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="AK30" s="5" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         </is>
       </c>
       <c r="AM30" s="5" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -13862,10 +13862,10 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="AD31" s="5" t="n">
-        <v>45770</v>
+        <v>45771</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -13893,10 +13893,10 @@
         </is>
       </c>
       <c r="AJ31" s="5" t="n">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="AK31" s="5" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         </is>
       </c>
       <c r="AM31" s="5" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45668</v>
+        <v>45669</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -14057,10 +14057,10 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>45716</v>
+        <v>45717</v>
       </c>
       <c r="AD32" s="5" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -14088,10 +14088,10 @@
         </is>
       </c>
       <c r="AJ32" s="5" t="n">
-        <v>45803</v>
+        <v>45804</v>
       </c>
       <c r="AK32" s="5" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         </is>
       </c>
       <c r="AM32" s="5" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -14251,10 +14251,10 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45590</v>
+        <v>45591</v>
       </c>
       <c r="AD33" s="5" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -14282,10 +14282,10 @@
         </is>
       </c>
       <c r="AJ33" s="5" t="n">
-        <v>46393</v>
+        <v>46394</v>
       </c>
       <c r="AK33" s="5" t="n">
-        <v>45740</v>
+        <v>45741</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         </is>
       </c>
       <c r="AM33" s="5" t="n">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
